--- a/COPIA PROGRAMADOR SEGUIMIENTO.xlsx
+++ b/COPIA PROGRAMADOR SEGUIMIENTO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\SEGUIMIENTO PRODUCCION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DAEFFED-16F8-493F-8477-678E2F5596C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741C1257-205E-465E-BBC6-56AEC62CE6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C06DA29B-B1D3-475F-97A6-5BB133A5B28B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13043" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13368" uniqueCount="784">
   <si>
     <t>PROCESO</t>
   </si>
@@ -2282,6 +2282,111 @@
   </si>
   <si>
     <t>CAMBIO DE TRAFOQUEMADO</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(10-10-2026)CR2</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(10-10-2026)CR5</t>
+  </si>
+  <si>
+    <t>cambio de poste buenos aires</t>
+  </si>
+  <si>
+    <t>cambio de protecciones</t>
+  </si>
+  <si>
+    <t>CAMBIO DE AISLADOR</t>
+  </si>
+  <si>
+    <t>recuperacion de linea rota bt</t>
+  </si>
+  <si>
+    <t>400915596 - 2 - 13-10</t>
+  </si>
+  <si>
+    <t>400915596 - 13-10</t>
+  </si>
+  <si>
+    <t>DI.PS.044.07.01(13-10-2026)</t>
+  </si>
+  <si>
+    <t>JHON WISTON</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(13-10-2026)CR3</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.02(13-10-2026)</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.02(13-10-2026)LINV308</t>
+  </si>
+  <si>
+    <t>APOYA CR2</t>
+  </si>
+  <si>
+    <t>DI.AR.007.02.04(13-10-2026)</t>
+  </si>
+  <si>
+    <t>Ibague</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(13-10-2026)</t>
+  </si>
+  <si>
+    <t>RETIRO DE POSTES EN ANCON</t>
+  </si>
+  <si>
+    <t>CAMBIO DE POSTE VDA LEONA</t>
+  </si>
+  <si>
+    <t>VALLE SAN JUAN</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(14-10-2026)CR1</t>
+  </si>
+  <si>
+    <t>Trabajos previos</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(14-10-2026)CR3</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.02(14-10-2026)</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(14-10-2026)LINV308</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(14-10-2026)CR4</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(14-10-2026)</t>
+  </si>
+  <si>
+    <t>cambio de poste vda san cayetano</t>
+  </si>
+  <si>
+    <t>cambio de poste vda patio bonito</t>
+  </si>
+  <si>
+    <t>cambio de aislador partido</t>
+  </si>
+  <si>
+    <t>ARREGLO DE PASE EN CAY</t>
+  </si>
+  <si>
+    <t>CIERRE DE PASE EN ESCOBAL</t>
+  </si>
+  <si>
+    <t>cambio de poste vda cural</t>
+  </si>
+  <si>
+    <t>cambio de poste en santa rosa</t>
   </si>
 </sst>
 </file>
@@ -2999,7 +3104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B1D2AE4-73A5-4A6B-9021-04AC9E1DF3F4}">
-  <dimension ref="A1:K1772"/>
+  <dimension ref="A1:K1818"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
@@ -25016,9 +25121,7 @@
         <v>14</v>
       </c>
       <c r="I740" s="3"/>
-      <c r="J740" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J740" s="3"/>
       <c r="K740" s="3"/>
     </row>
     <row r="741" spans="1:11" x14ac:dyDescent="0.25">
@@ -25404,9 +25507,7 @@
       <c r="I752" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="J752" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J752" s="3"/>
       <c r="K752" s="3"/>
     </row>
     <row r="753" spans="1:11" x14ac:dyDescent="0.25">
@@ -25819,9 +25920,7 @@
         <v>222</v>
       </c>
       <c r="I765" s="8"/>
-      <c r="J765" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J765" s="8"/>
       <c r="K765" s="8"/>
     </row>
     <row r="766" spans="1:11" x14ac:dyDescent="0.25">
@@ -27092,9 +27191,7 @@
       <c r="I804" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="J804" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J804" s="3"/>
       <c r="K804" s="4" t="s">
         <v>254</v>
       </c>
@@ -27331,9 +27428,7 @@
       <c r="I811" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="J811" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J811" s="8"/>
       <c r="K811" s="9" t="s">
         <v>254</v>
       </c>
@@ -30331,9 +30426,7 @@
       <c r="I903" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="J903" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J903" s="8"/>
       <c r="K903" s="9" t="s">
         <v>276</v>
       </c>
@@ -33092,9 +33185,7 @@
         <v>222</v>
       </c>
       <c r="I988" s="3"/>
-      <c r="J988" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J988" s="3"/>
       <c r="K988" s="4" t="s">
         <v>254</v>
       </c>
@@ -34427,9 +34518,7 @@
         <v>222</v>
       </c>
       <c r="I1029" s="8"/>
-      <c r="J1029" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1029" s="8"/>
       <c r="K1029" s="9" t="s">
         <v>254</v>
       </c>
@@ -34834,9 +34923,7 @@
         <v>222</v>
       </c>
       <c r="I1042" s="3"/>
-      <c r="J1042" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1042" s="3"/>
       <c r="K1042" s="4" t="s">
         <v>254</v>
       </c>
@@ -35651,9 +35738,7 @@
       <c r="I1067" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="J1067" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1067" s="8"/>
       <c r="K1067" s="9" t="s">
         <v>316</v>
       </c>
@@ -36232,9 +36317,7 @@
         <v>222</v>
       </c>
       <c r="I1084" s="3"/>
-      <c r="J1084" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1084" s="3"/>
       <c r="K1084" s="4" t="s">
         <v>316</v>
       </c>
@@ -36366,9 +36449,7 @@
         <v>222</v>
       </c>
       <c r="I1088" s="3"/>
-      <c r="J1088" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1088" s="3"/>
       <c r="K1088" s="4" t="s">
         <v>316</v>
       </c>
@@ -36877,9 +36958,7 @@
         <v>222</v>
       </c>
       <c r="I1103" s="8"/>
-      <c r="J1103" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1103" s="8"/>
       <c r="K1103" s="9" t="s">
         <v>316</v>
       </c>
@@ -37318,9 +37397,7 @@
         <v>222</v>
       </c>
       <c r="I1116" s="3"/>
-      <c r="J1116" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1116" s="3"/>
       <c r="K1116" s="4" t="s">
         <v>298</v>
       </c>
@@ -39110,9 +39187,7 @@
       <c r="I1170" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="J1170" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1170" s="3"/>
       <c r="K1170" s="4" t="s">
         <v>379</v>
       </c>
@@ -39619,9 +39694,7 @@
       <c r="I1185" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="J1185" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1185" s="8"/>
       <c r="K1185" s="9" t="s">
         <v>379</v>
       </c>
@@ -40118,9 +40191,7 @@
       <c r="I1200" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="J1200" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1200" s="3"/>
       <c r="K1200" s="4" t="s">
         <v>379</v>
       </c>
@@ -40458,9 +40529,7 @@
       <c r="I1210" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="J1210" s="14" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1210" s="13"/>
       <c r="K1210" s="14" t="s">
         <v>379</v>
       </c>
@@ -40559,9 +40628,7 @@
       <c r="I1213" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="J1213" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1213" s="8"/>
       <c r="K1213" s="9" t="s">
         <v>379</v>
       </c>
@@ -41804,9 +41871,7 @@
         <v>222</v>
       </c>
       <c r="I1250" s="3"/>
-      <c r="J1250" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1250" s="3"/>
       <c r="K1250" s="4" t="s">
         <v>254</v>
       </c>
@@ -42185,9 +42250,7 @@
       <c r="I1261" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="J1261" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1261" s="8"/>
       <c r="K1261" s="9" t="s">
         <v>254</v>
       </c>
@@ -42290,9 +42353,7 @@
       <c r="I1264" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="J1264" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1264" s="3"/>
       <c r="K1264" s="4" t="s">
         <v>254</v>
       </c>
@@ -42640,9 +42701,7 @@
       <c r="I1274" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="J1274" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1274" s="3"/>
       <c r="K1274" s="4" t="s">
         <v>254</v>
       </c>
@@ -43480,9 +43539,7 @@
       <c r="I1298" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="J1298" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1298" s="3"/>
       <c r="K1298" s="4" t="s">
         <v>254</v>
       </c>
@@ -44829,9 +44886,7 @@
       <c r="I1339" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="J1339" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1339" s="8"/>
       <c r="K1339" s="9" t="s">
         <v>254</v>
       </c>
@@ -45280,9 +45335,7 @@
       <c r="I1352" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="J1352" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1352" s="3"/>
       <c r="K1352" s="4" t="s">
         <v>254</v>
       </c>
@@ -45834,9 +45887,7 @@
       <c r="I1368" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="J1368" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1368" s="3"/>
       <c r="K1368" s="4" t="s">
         <v>254</v>
       </c>
@@ -45904,9 +45955,7 @@
       <c r="I1370" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="J1370" s="14" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1370" s="13"/>
       <c r="K1370" s="14" t="s">
         <v>254</v>
       </c>
@@ -45939,9 +45988,7 @@
       <c r="I1371" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="J1371" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1371" s="8"/>
       <c r="K1371" s="9" t="s">
         <v>254</v>
       </c>
@@ -46010,7 +46057,7 @@
         <v>511</v>
       </c>
       <c r="J1373" s="14" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1373" s="14" t="s">
         <v>236</v>
@@ -46255,7 +46302,7 @@
         <v>516</v>
       </c>
       <c r="J1380" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1380" s="4" t="s">
         <v>236</v>
@@ -46324,9 +46371,7 @@
       <c r="I1382" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="J1382" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1382" s="3"/>
       <c r="K1382" s="4" t="s">
         <v>254</v>
       </c>
@@ -46500,7 +46545,7 @@
         <v>511</v>
       </c>
       <c r="J1387" s="14" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1387" s="14" t="s">
         <v>236</v>
@@ -46780,7 +46825,7 @@
         <v>522</v>
       </c>
       <c r="J1395" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1395" s="9" t="s">
         <v>236</v>
@@ -46847,9 +46892,7 @@
         <v>222</v>
       </c>
       <c r="I1397" s="8"/>
-      <c r="J1397" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1397" s="8"/>
       <c r="K1397" s="9" t="s">
         <v>254</v>
       </c>
@@ -47268,9 +47311,7 @@
       <c r="I1410" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="J1410" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1410" s="3"/>
       <c r="K1410" s="4" t="s">
         <v>254</v>
       </c>
@@ -48123,7 +48164,7 @@
         <v>154</v>
       </c>
       <c r="J1436" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1436" s="4" t="s">
         <v>379</v>
@@ -48611,7 +48652,7 @@
         <v>154</v>
       </c>
       <c r="J1450" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1450" s="4" t="s">
         <v>379</v>
@@ -49066,7 +49107,7 @@
         <v>572</v>
       </c>
       <c r="J1463" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1463" s="9" t="s">
         <v>236</v>
@@ -49136,7 +49177,7 @@
         <v>572</v>
       </c>
       <c r="J1465" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1465" s="9" t="s">
         <v>236</v>
@@ -49171,7 +49212,7 @@
         <v>154</v>
       </c>
       <c r="J1466" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1466" s="4" t="s">
         <v>254</v>
@@ -49727,7 +49768,7 @@
         <v>154</v>
       </c>
       <c r="J1482" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1482" s="4" t="s">
         <v>586</v>
@@ -49831,9 +49872,7 @@
       <c r="I1485" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="J1485" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1485" s="8"/>
       <c r="K1485" s="9" t="s">
         <v>254</v>
       </c>
@@ -50318,7 +50357,7 @@
         <v>154</v>
       </c>
       <c r="J1499" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1499" s="9" t="s">
         <v>586</v>
@@ -51903,7 +51942,7 @@
         <v>624</v>
       </c>
       <c r="J1546" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1546" s="44"/>
     </row>
@@ -52488,7 +52527,7 @@
       </c>
       <c r="I1563" s="57"/>
       <c r="J1563" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1563" s="31" t="s">
         <v>254</v>
@@ -53005,7 +53044,7 @@
         <v>641</v>
       </c>
       <c r="J1578" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1578" s="7" t="s">
         <v>254</v>
@@ -53107,9 +53146,7 @@
       <c r="I1581" s="31" t="s">
         <v>644</v>
       </c>
-      <c r="J1581" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1581" s="8"/>
       <c r="K1581" s="31" t="s">
         <v>254</v>
       </c>
@@ -53557,7 +53594,7 @@
         <v>654</v>
       </c>
       <c r="J1594" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1594" s="7" t="s">
         <v>254</v>
@@ -53661,9 +53698,7 @@
       <c r="I1597" s="31" t="s">
         <v>658</v>
       </c>
-      <c r="J1597" s="9" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1597" s="8"/>
       <c r="K1597" s="31" t="s">
         <v>254</v>
       </c>
@@ -53992,7 +54027,7 @@
         <v>708</v>
       </c>
       <c r="J1607" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1607" s="31" t="s">
         <v>236</v>
@@ -54270,7 +54305,7 @@
         <v>654</v>
       </c>
       <c r="J1615" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1615" s="31" t="s">
         <v>254</v>
@@ -54374,9 +54409,7 @@
       <c r="I1618" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="J1618" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="J1618" s="3"/>
       <c r="K1618" s="7" t="s">
         <v>254</v>
       </c>
@@ -55829,7 +55862,7 @@
         <v>448</v>
       </c>
       <c r="J1662" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1662" s="4" t="s">
         <v>254</v>
@@ -56182,7 +56215,7 @@
         <v>685</v>
       </c>
       <c r="J1673" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1673" s="9" t="s">
         <v>236</v>
@@ -56217,7 +56250,7 @@
         <v>686</v>
       </c>
       <c r="J1674" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1674" s="4" t="s">
         <v>280</v>
@@ -56252,7 +56285,7 @@
         <v>687</v>
       </c>
       <c r="J1675" s="14" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1675" s="14" t="s">
         <v>280</v>
@@ -56320,7 +56353,7 @@
         <v>658</v>
       </c>
       <c r="J1677" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1677" s="9" t="s">
         <v>254</v>
@@ -56425,7 +56458,7 @@
         <v>658</v>
       </c>
       <c r="J1680" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1680" s="4" t="s">
         <v>254</v>
@@ -56549,7 +56582,7 @@
         <v>697</v>
       </c>
       <c r="J1684" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1684" s="4" t="s">
         <v>281</v>
@@ -56619,7 +56652,7 @@
         <v>699</v>
       </c>
       <c r="J1686" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1686" s="4" t="s">
         <v>303</v>
@@ -56654,7 +56687,7 @@
         <v>700</v>
       </c>
       <c r="J1687" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1687" s="9" t="s">
         <v>286</v>
@@ -56716,7 +56749,7 @@
         <v>686</v>
       </c>
       <c r="J1689" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1689" s="9" t="s">
         <v>280</v>
@@ -56751,7 +56784,7 @@
         <v>687</v>
       </c>
       <c r="J1690" s="14" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1690" s="14" t="s">
         <v>280</v>
@@ -56815,7 +56848,7 @@
         <v>658</v>
       </c>
       <c r="J1692" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1692" s="4" t="s">
         <v>254</v>
@@ -56920,7 +56953,7 @@
         <v>704</v>
       </c>
       <c r="J1695" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1695" s="9" t="s">
         <v>254</v>
@@ -56955,7 +56988,7 @@
         <v>704</v>
       </c>
       <c r="J1696" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1696" s="4" t="s">
         <v>254</v>
@@ -56990,7 +57023,7 @@
         <v>704</v>
       </c>
       <c r="J1697" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1697" s="9" t="s">
         <v>254</v>
@@ -57054,7 +57087,7 @@
         <v>709</v>
       </c>
       <c r="J1699" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1699" s="9" t="s">
         <v>306</v>
@@ -57089,7 +57122,7 @@
         <v>710</v>
       </c>
       <c r="J1700" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1700" s="4" t="s">
         <v>286</v>
@@ -57223,7 +57256,7 @@
         <v>715</v>
       </c>
       <c r="J1704" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1704" s="4" t="s">
         <v>353</v>
@@ -57287,7 +57320,7 @@
         <v>658</v>
       </c>
       <c r="J1706" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1706" s="4" t="s">
         <v>717</v>
@@ -57357,7 +57390,7 @@
         <v>720</v>
       </c>
       <c r="J1708" s="14" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1708" s="14" t="s">
         <v>717</v>
@@ -57460,9 +57493,11 @@
         <v>720</v>
       </c>
       <c r="J1711" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="K1711" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="K1711" s="14" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="1712" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1712" s="7" t="s">
@@ -57563,7 +57598,7 @@
         <v>725</v>
       </c>
       <c r="J1714" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1714" s="4" t="s">
         <v>389</v>
@@ -57598,7 +57633,7 @@
         <v>726</v>
       </c>
       <c r="J1715" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1715" s="9" t="s">
         <v>286</v>
@@ -57632,7 +57667,9 @@
       <c r="I1716" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="J1716" s="3"/>
+      <c r="J1716" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1716" s="4" t="s">
         <v>286</v>
       </c>
@@ -57666,7 +57703,7 @@
         <v>728</v>
       </c>
       <c r="J1717" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1717" s="9" t="s">
         <v>286</v>
@@ -57700,7 +57737,9 @@
       <c r="I1718" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="J1718" s="3"/>
+      <c r="J1718" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1718" s="4" t="s">
         <v>236</v>
       </c>
@@ -57872,7 +57911,7 @@
       </c>
       <c r="I1723" s="8"/>
       <c r="J1723" s="9" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="K1723" s="9" t="s">
         <v>717</v>
@@ -58249,7 +58288,9 @@
       <c r="I1735" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="J1735" s="8"/>
+      <c r="J1735" s="9" t="s">
+        <v>185</v>
+      </c>
       <c r="K1735" s="9" t="s">
         <v>236</v>
       </c>
@@ -58354,7 +58395,7 @@
       <c r="J1739" s="16"/>
       <c r="K1739" s="16"/>
     </row>
-    <row r="1740" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1740" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1740" s="7" t="s">
         <v>56</v>
       </c>
@@ -58370,12 +58411,20 @@
       <c r="E1740" s="52" t="s">
         <v>219</v>
       </c>
-      <c r="F1740" s="3"/>
-      <c r="G1740" s="3"/>
+      <c r="F1740" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1740" s="12" t="s">
+        <v>750</v>
+      </c>
       <c r="H1740" s="3"/>
       <c r="I1740" s="3"/>
-      <c r="J1740" s="3"/>
-      <c r="K1740" s="3"/>
+      <c r="J1740" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1740" s="4" t="s">
+        <v>719</v>
+      </c>
     </row>
     <row r="1741" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1741" s="31" t="s">
@@ -58405,7 +58454,9 @@
       <c r="I1741" s="9" t="s">
         <v>738</v>
       </c>
-      <c r="J1741" s="8"/>
+      <c r="J1741" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1741" s="9" t="s">
         <v>286</v>
       </c>
@@ -58435,7 +58486,7 @@
       <c r="J1742" s="16"/>
       <c r="K1742" s="16"/>
     </row>
-    <row r="1743" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1743" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1743" s="31" t="s">
         <v>56</v>
       </c>
@@ -58451,12 +58502,20 @@
       <c r="E1743" s="56" t="s">
         <v>579</v>
       </c>
-      <c r="F1743" s="8"/>
-      <c r="G1743" s="8"/>
+      <c r="F1743" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1743" s="21" t="s">
+        <v>751</v>
+      </c>
       <c r="H1743" s="8"/>
       <c r="I1743" s="8"/>
-      <c r="J1743" s="8"/>
-      <c r="K1743" s="8"/>
+      <c r="J1743" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1743" s="9" t="s">
+        <v>719</v>
+      </c>
     </row>
     <row r="1744" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1744" s="19" t="s">
@@ -58486,7 +58545,9 @@
       <c r="I1744" s="14" t="s">
         <v>739</v>
       </c>
-      <c r="J1744" s="13"/>
+      <c r="J1744" s="14" t="s">
+        <v>185</v>
+      </c>
       <c r="K1744" s="14" t="s">
         <v>236</v>
       </c>
@@ -58519,7 +58580,9 @@
       <c r="I1745" s="9" t="s">
         <v>740</v>
       </c>
-      <c r="J1745" s="8"/>
+      <c r="J1745" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1745" s="9" t="s">
         <v>265</v>
       </c>
@@ -58627,7 +58690,9 @@
       <c r="I1749" s="9" t="s">
         <v>741</v>
       </c>
-      <c r="J1749" s="8"/>
+      <c r="J1749" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1749" s="9" t="s">
         <v>272</v>
       </c>
@@ -58847,7 +58912,9 @@
       <c r="I1757" s="9" t="s">
         <v>744</v>
       </c>
-      <c r="J1757" s="8"/>
+      <c r="J1757" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1757" s="9" t="s">
         <v>265</v>
       </c>
@@ -58880,7 +58947,9 @@
       <c r="I1758" s="14" t="s">
         <v>745</v>
       </c>
-      <c r="J1758" s="13"/>
+      <c r="J1758" s="14" t="s">
+        <v>185</v>
+      </c>
       <c r="K1758" s="14" t="s">
         <v>236</v>
       </c>
@@ -58913,7 +58982,9 @@
       <c r="I1759" s="9" t="s">
         <v>746</v>
       </c>
-      <c r="J1759" s="8"/>
+      <c r="J1759" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1759" s="9" t="s">
         <v>303</v>
       </c>
@@ -59021,7 +59092,9 @@
       <c r="I1763" s="9" t="s">
         <v>746</v>
       </c>
-      <c r="J1763" s="8"/>
+      <c r="J1763" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1763" s="9" t="s">
         <v>286</v>
       </c>
@@ -59183,41 +59256,45 @@
       <c r="I1769" s="9" t="s">
         <v>747</v>
       </c>
-      <c r="J1769" s="8"/>
+      <c r="J1769" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1769" s="9" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="1770" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1770" s="19" t="s">
+      <c r="A1770" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="B1770" s="19" t="s">
+      <c r="B1770" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C1770" s="55">
         <v>46307</v>
       </c>
-      <c r="D1770" s="19" t="s">
+      <c r="D1770" s="52" t="s">
         <v>645</v>
       </c>
-      <c r="E1770" s="19" t="s">
+      <c r="E1770" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="F1770" s="14">
-        <v>400902730</v>
-      </c>
-      <c r="G1770" s="14">
-        <v>400902730</v>
-      </c>
-      <c r="H1770" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1770" s="14" t="s">
+      <c r="F1770" s="4">
+        <v>400902729</v>
+      </c>
+      <c r="G1770" s="4">
+        <v>400902729</v>
+      </c>
+      <c r="H1770" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1770" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="J1770" s="13"/>
-      <c r="K1770" s="14" t="s">
+      <c r="J1770" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1770" s="4" t="s">
         <v>236</v>
       </c>
     </row>
@@ -59274,14 +59351,1458 @@
       <c r="I1772" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="J1772" s="3"/>
+      <c r="J1772" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1772" s="4" t="s">
         <v>272</v>
       </c>
     </row>
+    <row r="1773" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1773" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1773" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1773" s="54">
+        <v>46308</v>
+      </c>
+      <c r="D1773" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1773" s="56" t="s">
+        <v>510</v>
+      </c>
+      <c r="F1773" s="9">
+        <v>400945029</v>
+      </c>
+      <c r="G1773" s="21">
+        <v>146614262</v>
+      </c>
+      <c r="H1773" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1773" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="J1773" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1773" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1774" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1774" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1774" s="55">
+        <v>46308</v>
+      </c>
+      <c r="D1774" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1774" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1774" s="4">
+        <v>400942462</v>
+      </c>
+      <c r="G1774" s="12">
+        <v>146612974</v>
+      </c>
+      <c r="H1774" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1774" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="J1774" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1774" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1775" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1775" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1775" s="54">
+        <v>46308</v>
+      </c>
+      <c r="D1775" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1775" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1775" s="16"/>
+      <c r="G1775" s="16"/>
+      <c r="H1775" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1775" s="16"/>
+      <c r="J1775" s="16"/>
+      <c r="K1775" s="16"/>
+    </row>
+    <row r="1776" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1776" s="52" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1776" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1776" s="55">
+        <v>46308</v>
+      </c>
+      <c r="D1776" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1776" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1776" s="7">
+        <v>400943005</v>
+      </c>
+      <c r="G1776" s="7">
+        <v>146600307</v>
+      </c>
+      <c r="H1776" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1776" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="J1776" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1776" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1777" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1777" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1777" s="54">
+        <v>46308</v>
+      </c>
+      <c r="D1777" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1777" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1777" s="7">
+        <v>400943009</v>
+      </c>
+      <c r="G1777" s="7">
+        <v>146604117</v>
+      </c>
+      <c r="H1777" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1777" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="J1777" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1777" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1778" s="52" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1778" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1778" s="55">
+        <v>46308</v>
+      </c>
+      <c r="D1778" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1778" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1778" s="4">
+        <v>400945025</v>
+      </c>
+      <c r="G1778" s="12">
+        <v>146609217</v>
+      </c>
+      <c r="H1778" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1778" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="J1778" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1778" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1779" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1779" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1779" s="54">
+        <v>46308</v>
+      </c>
+      <c r="D1779" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1779" s="56" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1779" s="9">
+        <v>400944211</v>
+      </c>
+      <c r="G1779" s="21">
+        <v>146608937</v>
+      </c>
+      <c r="H1779" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1779" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="J1779" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1779" s="9" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1780" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1780" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1780" s="55">
+        <v>46308</v>
+      </c>
+      <c r="D1780" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1780" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1780" s="14">
+        <v>400915596</v>
+      </c>
+      <c r="G1780" s="15" t="s">
+        <v>756</v>
+      </c>
+      <c r="H1780" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1780" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1780" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1780" s="14" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1781" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1781" s="56" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1781" s="54">
+        <v>46308</v>
+      </c>
+      <c r="D1781" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1781" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="F1781" s="9">
+        <v>400915596</v>
+      </c>
+      <c r="G1781" s="21" t="s">
+        <v>757</v>
+      </c>
+      <c r="H1781" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1781" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1781" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1781" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1782" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1782" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1782" s="55">
+        <v>46308</v>
+      </c>
+      <c r="D1782" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1782" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1782" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G1782" s="12" t="s">
+        <v>758</v>
+      </c>
+      <c r="H1782" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1782" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1782" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1782" s="4" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1783" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1783" s="31" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1783" s="54">
+        <v>46308</v>
+      </c>
+      <c r="D1783" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1783" s="56" t="s">
+        <v>759</v>
+      </c>
+      <c r="F1783" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1783" s="21" t="s">
+        <v>760</v>
+      </c>
+      <c r="H1783" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1783" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1783" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1783" s="9" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1784" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1784" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1784" s="55">
+        <v>46308</v>
+      </c>
+      <c r="D1784" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1784" s="52" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1784" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="G1784" s="12" t="s">
+        <v>761</v>
+      </c>
+      <c r="H1784" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1784" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1784" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1784" s="4" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1785" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1785" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1785" s="54">
+        <v>46308</v>
+      </c>
+      <c r="D1785" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1785" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1785" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="G1785" s="21" t="s">
+        <v>762</v>
+      </c>
+      <c r="H1785" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1785" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="J1785" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1785" s="9" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1786" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1786" s="52" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1786" s="55">
+        <v>46308</v>
+      </c>
+      <c r="D1786" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1786" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1786" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="G1786" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="H1786" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1786" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1786" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1786" s="4" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1787" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1787" s="31" t="s">
+        <v>578</v>
+      </c>
+      <c r="C1787" s="54">
+        <v>46308</v>
+      </c>
+      <c r="D1787" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1787" s="56" t="s">
+        <v>579</v>
+      </c>
+      <c r="F1787" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1787" s="21" t="s">
+        <v>766</v>
+      </c>
+      <c r="H1787" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1787" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1787" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1787" s="9" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1788" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1788" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1788" s="55">
+        <v>46309</v>
+      </c>
+      <c r="D1788" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1788" s="19" t="s">
+        <v>510</v>
+      </c>
+      <c r="F1788" s="13"/>
+      <c r="G1788" s="13"/>
+      <c r="H1788" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1788" s="14" t="s">
+        <v>767</v>
+      </c>
+      <c r="J1788" s="13"/>
+      <c r="K1788" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1789" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1789" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1789" s="54">
+        <v>46309</v>
+      </c>
+      <c r="D1789" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1789" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1789" s="7">
+        <v>400945032</v>
+      </c>
+      <c r="G1789" s="21">
+        <v>146614161</v>
+      </c>
+      <c r="H1789" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1789" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="J1789" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1789" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1790" s="52" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1790" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1790" s="55">
+        <v>46309</v>
+      </c>
+      <c r="D1790" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1790" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1790" s="4">
+        <v>400943840</v>
+      </c>
+      <c r="G1790" s="12">
+        <v>146606293</v>
+      </c>
+      <c r="H1790" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1790" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="J1790" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1790" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1791" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1791" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1791" s="54">
+        <v>46309</v>
+      </c>
+      <c r="D1791" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1791" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1791" s="34"/>
+      <c r="G1791" s="13"/>
+      <c r="H1791" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1791" s="14" t="s">
+        <v>767</v>
+      </c>
+      <c r="J1791" s="13"/>
+      <c r="K1791" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1792" s="52" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1792" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1792" s="55">
+        <v>46309</v>
+      </c>
+      <c r="D1792" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1792" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1792" s="7">
+        <v>400945034</v>
+      </c>
+      <c r="G1792" s="7">
+        <v>146614961</v>
+      </c>
+      <c r="H1792" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1792" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="J1792" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1792" s="4" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1793" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1793" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1793" s="54">
+        <v>46309</v>
+      </c>
+      <c r="D1793" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1793" s="56" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1793" s="8"/>
+      <c r="G1793" s="8"/>
+      <c r="H1793" s="8"/>
+      <c r="I1793" s="8"/>
+      <c r="J1793" s="8"/>
+      <c r="K1793" s="8"/>
+    </row>
+    <row r="1794" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1794" s="52" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1794" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1794" s="55">
+        <v>46309</v>
+      </c>
+      <c r="D1794" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1794" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1794" s="4">
+        <v>400945391</v>
+      </c>
+      <c r="G1794" s="12">
+        <v>146604773</v>
+      </c>
+      <c r="H1794" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1794" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="J1794" s="3"/>
+      <c r="K1794" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1795" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1795" s="56" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1795" s="54">
+        <v>46309</v>
+      </c>
+      <c r="D1795" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1795" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="F1795" s="8"/>
+      <c r="G1795" s="8"/>
+      <c r="H1795" s="8"/>
+      <c r="I1795" s="8"/>
+      <c r="J1795" s="8"/>
+      <c r="K1795" s="8"/>
+    </row>
+    <row r="1796" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1796" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1796" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1796" s="55">
+        <v>46309</v>
+      </c>
+      <c r="D1796" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1796" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1796" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1796" s="12" t="s">
+        <v>770</v>
+      </c>
+      <c r="H1796" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1796" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="J1796" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1796" s="4" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1797" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1797" s="31" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1797" s="54">
+        <v>46309</v>
+      </c>
+      <c r="D1797" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1797" s="56" t="s">
+        <v>759</v>
+      </c>
+      <c r="F1797" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1797" s="21" t="s">
+        <v>772</v>
+      </c>
+      <c r="H1797" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1797" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="J1797" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1797" s="9" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1798" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1798" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1798" s="55">
+        <v>46309</v>
+      </c>
+      <c r="D1798" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1798" s="52" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1798" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="G1798" s="12" t="s">
+        <v>773</v>
+      </c>
+      <c r="H1798" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1798" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="J1798" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1798" s="4" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1799" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1799" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1799" s="54">
+        <v>46309</v>
+      </c>
+      <c r="D1799" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1799" s="56" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1799" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1799" s="21" t="s">
+        <v>774</v>
+      </c>
+      <c r="H1799" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1799" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="J1799" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1799" s="9" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1800" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1800" s="52" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1800" s="55">
+        <v>46309</v>
+      </c>
+      <c r="D1800" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1800" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1800" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1800" s="12" t="s">
+        <v>775</v>
+      </c>
+      <c r="H1800" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1800" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="J1800" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1800" s="4" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1801" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1801" s="31" t="s">
+        <v>578</v>
+      </c>
+      <c r="C1801" s="54">
+        <v>46309</v>
+      </c>
+      <c r="D1801" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1801" s="56" t="s">
+        <v>579</v>
+      </c>
+      <c r="F1801" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1801" s="21" t="s">
+        <v>776</v>
+      </c>
+      <c r="H1801" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1801" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="J1801" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1801" s="9" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1802" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1802" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1802" s="55">
+        <v>46310</v>
+      </c>
+      <c r="D1802" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1802" s="19" t="s">
+        <v>510</v>
+      </c>
+      <c r="F1802" s="13"/>
+      <c r="G1802" s="13"/>
+      <c r="H1802" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1802" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="J1802" s="13"/>
+      <c r="K1802" s="13"/>
+    </row>
+    <row r="1803" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1803" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1803" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1803" s="54">
+        <v>46310</v>
+      </c>
+      <c r="D1803" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1803" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1803" s="20">
+        <v>400944037</v>
+      </c>
+      <c r="G1803" s="20">
+        <v>146607379</v>
+      </c>
+      <c r="H1803" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1803" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="J1803" s="8"/>
+      <c r="K1803" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1804" s="52" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1804" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1804" s="55">
+        <v>46310</v>
+      </c>
+      <c r="D1804" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1804" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1804" s="20">
+        <v>400944892</v>
+      </c>
+      <c r="G1804" s="23">
+        <v>146612784</v>
+      </c>
+      <c r="H1804" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1804" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="J1804" s="3"/>
+      <c r="K1804" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1805" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1805" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1805" s="54">
+        <v>46310</v>
+      </c>
+      <c r="D1805" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1805" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1805" s="9">
+        <v>146616503</v>
+      </c>
+      <c r="G1805" s="21">
+        <v>146616503</v>
+      </c>
+      <c r="H1805" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1805" s="9" t="s">
+        <v>779</v>
+      </c>
+      <c r="J1805" s="8"/>
+      <c r="K1805" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1806" s="52" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1806" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1806" s="55">
+        <v>46310</v>
+      </c>
+      <c r="D1806" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1806" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1806" s="4">
+        <v>146616718</v>
+      </c>
+      <c r="G1806" s="4">
+        <v>146616718</v>
+      </c>
+      <c r="H1806" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1806" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="J1806" s="3"/>
+      <c r="K1806" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1807" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1807" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1807" s="54">
+        <v>46310</v>
+      </c>
+      <c r="D1807" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1807" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1807" s="9">
+        <v>146616789</v>
+      </c>
+      <c r="G1807" s="9">
+        <v>146616789</v>
+      </c>
+      <c r="H1807" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1807" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="J1807" s="8"/>
+      <c r="K1807" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1808" s="52" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1808" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1808" s="55">
+        <v>46310</v>
+      </c>
+      <c r="D1808" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1808" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1808" s="4">
+        <v>146616750</v>
+      </c>
+      <c r="G1808" s="4">
+        <v>146616750</v>
+      </c>
+      <c r="H1808" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1808" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="J1808" s="3"/>
+      <c r="K1808" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1809" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1809" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1809" s="54">
+        <v>46310</v>
+      </c>
+      <c r="D1809" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1809" s="56" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1809" s="7">
+        <v>400944213</v>
+      </c>
+      <c r="G1809" s="21">
+        <v>146607477</v>
+      </c>
+      <c r="H1809" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1809" s="9" t="s">
+        <v>782</v>
+      </c>
+      <c r="J1809" s="8"/>
+      <c r="K1809" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1810" s="52" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1810" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1810" s="55">
+        <v>46310</v>
+      </c>
+      <c r="D1810" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1810" s="52" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1810" s="3"/>
+      <c r="G1810" s="3"/>
+      <c r="H1810" s="3"/>
+      <c r="I1810" s="3"/>
+      <c r="J1810" s="3"/>
+      <c r="K1810" s="3"/>
+    </row>
+    <row r="1811" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1811" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1811" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1811" s="54">
+        <v>46310</v>
+      </c>
+      <c r="D1811" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1811" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1811" s="9">
+        <v>400945390</v>
+      </c>
+      <c r="G1811" s="21">
+        <v>145565949</v>
+      </c>
+      <c r="H1811" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1811" s="9" t="s">
+        <v>783</v>
+      </c>
+      <c r="J1811" s="8"/>
+      <c r="K1811" s="9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1812" s="52" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1812" s="52" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1812" s="55">
+        <v>46310</v>
+      </c>
+      <c r="D1812" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1812" s="52" t="s">
+        <v>335</v>
+      </c>
+      <c r="F1812" s="3"/>
+      <c r="G1812" s="3"/>
+      <c r="H1812" s="3"/>
+      <c r="I1812" s="3"/>
+      <c r="J1812" s="3"/>
+      <c r="K1812" s="3"/>
+    </row>
+    <row r="1813" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1813" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1813" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1813" s="54">
+        <v>46310</v>
+      </c>
+      <c r="D1813" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1813" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1813" s="8"/>
+      <c r="G1813" s="8"/>
+      <c r="H1813" s="8"/>
+      <c r="I1813" s="8"/>
+      <c r="J1813" s="8"/>
+      <c r="K1813" s="8"/>
+    </row>
+    <row r="1814" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1814" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1814" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1814" s="55">
+        <v>46310</v>
+      </c>
+      <c r="D1814" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1814" s="52" t="s">
+        <v>759</v>
+      </c>
+      <c r="F1814" s="3"/>
+      <c r="G1814" s="3"/>
+      <c r="H1814" s="3"/>
+      <c r="I1814" s="3"/>
+      <c r="J1814" s="3"/>
+      <c r="K1814" s="3"/>
+    </row>
+    <row r="1815" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1815" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1815" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1815" s="54">
+        <v>46310</v>
+      </c>
+      <c r="D1815" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1815" s="56" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1815" s="8"/>
+      <c r="G1815" s="8"/>
+      <c r="H1815" s="8"/>
+      <c r="I1815" s="8"/>
+      <c r="J1815" s="8"/>
+      <c r="K1815" s="8"/>
+    </row>
+    <row r="1816" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1816" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1816" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1816" s="55">
+        <v>46310</v>
+      </c>
+      <c r="D1816" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1816" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1816" s="3"/>
+      <c r="G1816" s="3"/>
+      <c r="H1816" s="3"/>
+      <c r="I1816" s="3"/>
+      <c r="J1816" s="3"/>
+      <c r="K1816" s="3"/>
+    </row>
+    <row r="1817" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1817" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1817" s="56" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1817" s="54">
+        <v>46310</v>
+      </c>
+      <c r="D1817" s="56" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1817" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1817" s="8"/>
+      <c r="G1817" s="8"/>
+      <c r="H1817" s="8"/>
+      <c r="I1817" s="8"/>
+      <c r="J1817" s="8"/>
+      <c r="K1817" s="8"/>
+    </row>
+    <row r="1818" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1818" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1818" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="C1818" s="55">
+        <v>46310</v>
+      </c>
+      <c r="D1818" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1818" s="52" t="s">
+        <v>579</v>
+      </c>
+      <c r="F1818" s="3"/>
+      <c r="G1818" s="3"/>
+      <c r="H1818" s="3"/>
+      <c r="I1818" s="3"/>
+      <c r="J1818" s="3"/>
+      <c r="K1818" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F1410" r:id="rId1" display="http://di.ps/" xr:uid="{216DF313-478E-4086-B18D-5F3E102713E6}"/>
+    <hyperlink ref="F1410" r:id="rId1" display="http://di.ps/" xr:uid="{3F374B45-1231-48CF-9AFE-3A44DBF64903}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/COPIA PROGRAMADOR SEGUIMIENTO.xlsx
+++ b/COPIA PROGRAMADOR SEGUIMIENTO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\SEGUIMIENTO PRODUCCION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741C1257-205E-465E-BBC6-56AEC62CE6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C36984-4562-4F11-B241-4FD1F24959C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C06DA29B-B1D3-475F-97A6-5BB133A5B28B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13368" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13809" uniqueCount="815">
   <si>
     <t>PROCESO</t>
   </si>
@@ -2387,13 +2387,106 @@
   </si>
   <si>
     <t>cambio de poste en santa rosa</t>
+  </si>
+  <si>
+    <t>PROGRAMADOS - PROPUESTA 1</t>
+  </si>
+  <si>
+    <t>PROGRAMADOS - LA CIMA</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(15-10-2026)CR1</t>
+  </si>
+  <si>
+    <t>APOYA CR3</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(15-10-2026)</t>
+  </si>
+  <si>
+    <t>CONSIGNA MT CHUCUNI</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.02(15-10-2026)</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.02(15-10-2026)LINV308</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(15-10-2026)CR4</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.02(15-10-2026)CR5</t>
+  </si>
+  <si>
+    <t>RECUPERACION DE LINEA ROTA BT - PARA CANCELAR</t>
+  </si>
+  <si>
+    <t>RECUPERACION DE LINEA ROTA BT</t>
+  </si>
+  <si>
+    <t>INSTALACION DE RETENIDA</t>
+  </si>
+  <si>
+    <t>ARREGLO DE PASE MT</t>
+  </si>
+  <si>
+    <t>RECUPERACION DE LINEA ROTA BT - EJECUTA EFREY</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.01.04.01(16-10-2026)CR1</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(16-10-2026)</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.02(16-10-2026)CR2</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.01.04.01(16-10-2026)</t>
+  </si>
+  <si>
+    <t>Apoya proyecto programados</t>
+  </si>
+  <si>
+    <t>APOYO EN BOLV</t>
+  </si>
+  <si>
+    <t>CAMBIO DE RECONECTADOR</t>
+  </si>
+  <si>
+    <t>RECUPERACION DE LINEAS ROTAS BT</t>
+  </si>
+  <si>
+    <t>APOYO BOLV</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.01.04.01(19-10-2026)CR1</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.06.03(19-10-2026)</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.10.01</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.10.01(19-10-2026)</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.01.04.01(19-10-2026)</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.01.04.01(19-10-2026)CR4</t>
+  </si>
+  <si>
+    <t>DI.RP.200.01.03.02.10.01(19-10-2026)CR5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2496,16 +2589,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2578,6 +2663,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF00FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2603,11 +2694,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2759,9 +2849,6 @@
     <xf numFmtId="14" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2789,9 +2876,14 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3104,7 +3196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B1D2AE4-73A5-4A6B-9021-04AC9E1DF3F4}">
-  <dimension ref="A1:K1818"/>
+  <dimension ref="A1:K1874"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
@@ -25121,7 +25213,9 @@
         <v>14</v>
       </c>
       <c r="I740" s="3"/>
-      <c r="J740" s="3"/>
+      <c r="J740" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K740" s="3"/>
     </row>
     <row r="741" spans="1:11" x14ac:dyDescent="0.25">
@@ -25507,7 +25601,9 @@
       <c r="I752" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="J752" s="3"/>
+      <c r="J752" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K752" s="3"/>
     </row>
     <row r="753" spans="1:11" x14ac:dyDescent="0.25">
@@ -25920,7 +26016,9 @@
         <v>222</v>
       </c>
       <c r="I765" s="8"/>
-      <c r="J765" s="8"/>
+      <c r="J765" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K765" s="8"/>
     </row>
     <row r="766" spans="1:11" x14ac:dyDescent="0.25">
@@ -27191,7 +27289,9 @@
       <c r="I804" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="J804" s="3"/>
+      <c r="J804" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K804" s="4" t="s">
         <v>254</v>
       </c>
@@ -27428,7 +27528,9 @@
       <c r="I811" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="J811" s="8"/>
+      <c r="J811" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K811" s="9" t="s">
         <v>254</v>
       </c>
@@ -30426,7 +30528,9 @@
       <c r="I903" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="J903" s="8"/>
+      <c r="J903" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K903" s="9" t="s">
         <v>276</v>
       </c>
@@ -33185,7 +33289,9 @@
         <v>222</v>
       </c>
       <c r="I988" s="3"/>
-      <c r="J988" s="3"/>
+      <c r="J988" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K988" s="4" t="s">
         <v>254</v>
       </c>
@@ -34518,7 +34624,9 @@
         <v>222</v>
       </c>
       <c r="I1029" s="8"/>
-      <c r="J1029" s="8"/>
+      <c r="J1029" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1029" s="9" t="s">
         <v>254</v>
       </c>
@@ -34923,7 +35031,9 @@
         <v>222</v>
       </c>
       <c r="I1042" s="3"/>
-      <c r="J1042" s="3"/>
+      <c r="J1042" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1042" s="4" t="s">
         <v>254</v>
       </c>
@@ -35738,7 +35848,9 @@
       <c r="I1067" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="J1067" s="8"/>
+      <c r="J1067" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1067" s="9" t="s">
         <v>316</v>
       </c>
@@ -36307,7 +36419,7 @@
       <c r="E1084" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="F1084" s="45" t="s">
+      <c r="F1084" s="4" t="s">
         <v>215</v>
       </c>
       <c r="G1084" s="4" t="s">
@@ -36317,7 +36429,9 @@
         <v>222</v>
       </c>
       <c r="I1084" s="3"/>
-      <c r="J1084" s="3"/>
+      <c r="J1084" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1084" s="4" t="s">
         <v>316</v>
       </c>
@@ -36439,7 +36553,7 @@
       <c r="E1088" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F1088" s="45" t="s">
+      <c r="F1088" s="4" t="s">
         <v>215</v>
       </c>
       <c r="G1088" s="4" t="s">
@@ -36449,7 +36563,9 @@
         <v>222</v>
       </c>
       <c r="I1088" s="3"/>
-      <c r="J1088" s="3"/>
+      <c r="J1088" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1088" s="4" t="s">
         <v>316</v>
       </c>
@@ -36948,7 +37064,7 @@
       <c r="E1103" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F1103" s="45" t="s">
+      <c r="F1103" s="9" t="s">
         <v>215</v>
       </c>
       <c r="G1103" s="9" t="s">
@@ -36958,7 +37074,9 @@
         <v>222</v>
       </c>
       <c r="I1103" s="8"/>
-      <c r="J1103" s="8"/>
+      <c r="J1103" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1103" s="9" t="s">
         <v>316</v>
       </c>
@@ -37387,7 +37505,7 @@
       <c r="E1116" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F1116" s="45" t="s">
+      <c r="F1116" s="4" t="s">
         <v>215</v>
       </c>
       <c r="G1116" s="4" t="s">
@@ -37397,7 +37515,9 @@
         <v>222</v>
       </c>
       <c r="I1116" s="3"/>
-      <c r="J1116" s="3"/>
+      <c r="J1116" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1116" s="4" t="s">
         <v>298</v>
       </c>
@@ -39187,7 +39307,9 @@
       <c r="I1170" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="J1170" s="3"/>
+      <c r="J1170" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1170" s="4" t="s">
         <v>379</v>
       </c>
@@ -39694,7 +39816,9 @@
       <c r="I1185" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="J1185" s="8"/>
+      <c r="J1185" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1185" s="9" t="s">
         <v>379</v>
       </c>
@@ -40191,7 +40315,9 @@
       <c r="I1200" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="J1200" s="3"/>
+      <c r="J1200" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1200" s="4" t="s">
         <v>379</v>
       </c>
@@ -40529,7 +40655,9 @@
       <c r="I1210" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="J1210" s="13"/>
+      <c r="J1210" s="14" t="s">
+        <v>16</v>
+      </c>
       <c r="K1210" s="14" t="s">
         <v>379</v>
       </c>
@@ -40628,7 +40756,9 @@
       <c r="I1213" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="J1213" s="8"/>
+      <c r="J1213" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1213" s="9" t="s">
         <v>379</v>
       </c>
@@ -41871,7 +42001,9 @@
         <v>222</v>
       </c>
       <c r="I1250" s="3"/>
-      <c r="J1250" s="3"/>
+      <c r="J1250" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1250" s="4" t="s">
         <v>254</v>
       </c>
@@ -42250,7 +42382,9 @@
       <c r="I1261" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="J1261" s="8"/>
+      <c r="J1261" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1261" s="9" t="s">
         <v>254</v>
       </c>
@@ -42353,7 +42487,9 @@
       <c r="I1264" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="J1264" s="3"/>
+      <c r="J1264" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1264" s="4" t="s">
         <v>254</v>
       </c>
@@ -42701,7 +42837,9 @@
       <c r="I1274" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="J1274" s="3"/>
+      <c r="J1274" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1274" s="4" t="s">
         <v>254</v>
       </c>
@@ -43539,7 +43677,9 @@
       <c r="I1298" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="J1298" s="3"/>
+      <c r="J1298" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1298" s="4" t="s">
         <v>254</v>
       </c>
@@ -44886,7 +45026,9 @@
       <c r="I1339" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="J1339" s="8"/>
+      <c r="J1339" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1339" s="9" t="s">
         <v>254</v>
       </c>
@@ -45335,7 +45477,9 @@
       <c r="I1352" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="J1352" s="3"/>
+      <c r="J1352" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1352" s="4" t="s">
         <v>254</v>
       </c>
@@ -45887,7 +46031,9 @@
       <c r="I1368" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="J1368" s="3"/>
+      <c r="J1368" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1368" s="4" t="s">
         <v>254</v>
       </c>
@@ -45955,7 +46101,9 @@
       <c r="I1370" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="J1370" s="13"/>
+      <c r="J1370" s="14" t="s">
+        <v>16</v>
+      </c>
       <c r="K1370" s="14" t="s">
         <v>254</v>
       </c>
@@ -45988,7 +46136,9 @@
       <c r="I1371" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="J1371" s="8"/>
+      <c r="J1371" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1371" s="9" t="s">
         <v>254</v>
       </c>
@@ -46371,7 +46521,9 @@
       <c r="I1382" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="J1382" s="3"/>
+      <c r="J1382" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1382" s="4" t="s">
         <v>254</v>
       </c>
@@ -46892,7 +47044,9 @@
         <v>222</v>
       </c>
       <c r="I1397" s="8"/>
-      <c r="J1397" s="8"/>
+      <c r="J1397" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1397" s="9" t="s">
         <v>254</v>
       </c>
@@ -47299,7 +47453,7 @@
       <c r="E1410" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F1410" s="51" t="s">
+      <c r="F1410" s="4" t="s">
         <v>377</v>
       </c>
       <c r="G1410" s="4" t="s">
@@ -47311,7 +47465,9 @@
       <c r="I1410" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="J1410" s="3"/>
+      <c r="J1410" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1410" s="4" t="s">
         <v>254</v>
       </c>
@@ -49872,7 +50028,9 @@
       <c r="I1485" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="J1485" s="8"/>
+      <c r="J1485" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1485" s="9" t="s">
         <v>254</v>
       </c>
@@ -49960,7 +50118,7 @@
       <c r="D1488" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="E1488" s="52" t="s">
+      <c r="E1488" s="51" t="s">
         <v>510</v>
       </c>
       <c r="F1488" s="4">
@@ -50094,7 +50252,7 @@
       <c r="B1492" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C1492" s="53">
+      <c r="C1492" s="52">
         <v>46290</v>
       </c>
       <c r="D1492" s="33" t="s">
@@ -50551,7 +50709,7 @@
       <c r="D1505" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="E1505" s="52" t="s">
+      <c r="E1505" s="51" t="s">
         <v>510</v>
       </c>
       <c r="F1505" s="4">
@@ -51539,7 +51697,7 @@
       <c r="B1535" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C1535" s="54">
+      <c r="C1535" s="53">
         <v>46293</v>
       </c>
       <c r="D1535" s="33" t="s">
@@ -51568,19 +51726,19 @@
       </c>
     </row>
     <row r="1536" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1536" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1536" s="52" t="s">
+      <c r="A1536" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1536" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="C1536" s="55">
+      <c r="C1536" s="54">
         <v>46293</v>
       </c>
-      <c r="D1536" s="52" t="s">
+      <c r="D1536" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="E1536" s="52" t="s">
+      <c r="E1536" s="51" t="s">
         <v>510</v>
       </c>
       <c r="F1536" s="7">
@@ -51589,16 +51747,16 @@
       <c r="G1536" s="7">
         <v>145564914</v>
       </c>
-      <c r="H1536" s="52" t="s">
+      <c r="H1536" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="I1536" s="52" t="s">
+      <c r="I1536" s="51" t="s">
         <v>618</v>
       </c>
       <c r="J1536" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K1536" s="52" t="s">
+      <c r="K1536" s="51" t="s">
         <v>236</v>
       </c>
     </row>
@@ -51609,13 +51767,13 @@
       <c r="B1537" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C1537" s="54">
+      <c r="C1537" s="53">
         <v>46293</v>
       </c>
       <c r="D1537" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="E1537" s="56" t="s">
+      <c r="E1537" s="55" t="s">
         <v>18</v>
       </c>
       <c r="F1537" s="31">
@@ -51644,7 +51802,7 @@
       <c r="B1538" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C1538" s="55">
+      <c r="C1538" s="54">
         <v>46293</v>
       </c>
       <c r="D1538" s="33" t="s">
@@ -51679,7 +51837,7 @@
       <c r="B1539" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="C1539" s="54">
+      <c r="C1539" s="53">
         <v>46293</v>
       </c>
       <c r="D1539" s="33" t="s">
@@ -51714,7 +51872,7 @@
       <c r="B1540" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="C1540" s="55">
+      <c r="C1540" s="54">
         <v>46293</v>
       </c>
       <c r="D1540" s="33" t="s">
@@ -51743,19 +51901,19 @@
       </c>
     </row>
     <row r="1541" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1541" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1541" s="56" t="s">
+      <c r="A1541" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1541" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1541" s="54">
+      <c r="C1541" s="53">
         <v>46293</v>
       </c>
-      <c r="D1541" s="56" t="s">
+      <c r="D1541" s="55" t="s">
         <v>374</v>
       </c>
-      <c r="E1541" s="56" t="s">
+      <c r="E1541" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1541" s="31">
@@ -51764,7 +51922,7 @@
       <c r="G1541" s="31">
         <v>145564945</v>
       </c>
-      <c r="H1541" s="56" t="s">
+      <c r="H1541" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1541" s="31" t="s">
@@ -51784,7 +51942,7 @@
       <c r="B1542" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="C1542" s="55">
+      <c r="C1542" s="54">
         <v>46293</v>
       </c>
       <c r="D1542" s="33" t="s">
@@ -51819,7 +51977,7 @@
       <c r="B1543" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C1543" s="54">
+      <c r="C1543" s="53">
         <v>46293</v>
       </c>
       <c r="D1543" s="33" t="s">
@@ -51848,19 +52006,19 @@
       </c>
     </row>
     <row r="1544" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1544" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1544" s="52" t="s">
+      <c r="A1544" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1544" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C1544" s="55">
+      <c r="C1544" s="54">
         <v>46293</v>
       </c>
-      <c r="D1544" s="52" t="s">
+      <c r="D1544" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="E1544" s="52" t="s">
+      <c r="E1544" s="51" t="s">
         <v>25</v>
       </c>
       <c r="F1544" s="7">
@@ -51869,7 +52027,7 @@
       <c r="G1544" s="7">
         <v>145562983</v>
       </c>
-      <c r="H1544" s="52" t="s">
+      <c r="H1544" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1544" s="7" t="s">
@@ -51883,19 +52041,19 @@
       </c>
     </row>
     <row r="1545" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1545" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1545" s="56" t="s">
+      <c r="A1545" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1545" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="C1545" s="54">
+      <c r="C1545" s="53">
         <v>46293</v>
       </c>
-      <c r="D1545" s="56" t="s">
+      <c r="D1545" s="55" t="s">
         <v>374</v>
       </c>
-      <c r="E1545" s="56" t="s">
+      <c r="E1545" s="55" t="s">
         <v>335</v>
       </c>
       <c r="F1545" s="31">
@@ -51904,29 +52062,29 @@
       <c r="G1545" s="31">
         <v>400915496</v>
       </c>
-      <c r="H1545" s="56" t="s">
+      <c r="H1545" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="I1545" s="57"/>
+      <c r="I1545" s="56"/>
       <c r="J1545" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K1545" s="57"/>
+      <c r="K1545" s="56"/>
     </row>
     <row r="1546" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1546" s="52" t="s">
+      <c r="A1546" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B1546" s="52" t="s">
+      <c r="B1546" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="C1546" s="55">
+      <c r="C1546" s="54">
         <v>46293</v>
       </c>
-      <c r="D1546" s="52" t="s">
+      <c r="D1546" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="E1546" s="52" t="s">
+      <c r="E1546" s="51" t="s">
         <v>23</v>
       </c>
       <c r="F1546" s="7" t="s">
@@ -51935,7 +52093,7 @@
       <c r="G1546" s="7" t="s">
         <v>623</v>
       </c>
-      <c r="H1546" s="52" t="s">
+      <c r="H1546" s="51" t="s">
         <v>222</v>
       </c>
       <c r="I1546" s="7" t="s">
@@ -51953,13 +52111,13 @@
       <c r="B1547" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="C1547" s="54">
+      <c r="C1547" s="53">
         <v>46293</v>
       </c>
       <c r="D1547" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="E1547" s="56" t="s">
+      <c r="E1547" s="55" t="s">
         <v>310</v>
       </c>
       <c r="F1547" s="31" t="s">
@@ -51988,13 +52146,13 @@
       <c r="B1548" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C1548" s="55">
+      <c r="C1548" s="54">
         <v>46293</v>
       </c>
       <c r="D1548" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="E1548" s="52" t="s">
+      <c r="E1548" s="51" t="s">
         <v>219</v>
       </c>
       <c r="F1548" s="7" t="s">
@@ -52023,13 +52181,13 @@
       <c r="B1549" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C1549" s="54">
+      <c r="C1549" s="53">
         <v>46293</v>
       </c>
       <c r="D1549" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="E1549" s="56" t="s">
+      <c r="E1549" s="55" t="s">
         <v>29</v>
       </c>
       <c r="F1549" s="31">
@@ -52058,13 +52216,13 @@
       <c r="B1550" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C1550" s="55">
+      <c r="C1550" s="54">
         <v>46293</v>
       </c>
       <c r="D1550" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="E1550" s="52" t="s">
+      <c r="E1550" s="51" t="s">
         <v>29</v>
       </c>
       <c r="F1550" s="7">
@@ -52087,19 +52245,19 @@
       </c>
     </row>
     <row r="1551" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1551" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1551" s="56" t="s">
+      <c r="A1551" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1551" s="55" t="s">
         <v>501</v>
       </c>
-      <c r="C1551" s="54">
+      <c r="C1551" s="53">
         <v>46293</v>
       </c>
-      <c r="D1551" s="56" t="s">
+      <c r="D1551" s="55" t="s">
         <v>374</v>
       </c>
-      <c r="E1551" s="56" t="s">
+      <c r="E1551" s="55" t="s">
         <v>13</v>
       </c>
       <c r="F1551" s="31">
@@ -52108,7 +52266,7 @@
       <c r="G1551" s="31">
         <v>146591385</v>
       </c>
-      <c r="H1551" s="56" t="s">
+      <c r="H1551" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1551" s="31" t="s">
@@ -52117,7 +52275,7 @@
       <c r="J1551" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K1551" s="56" t="s">
+      <c r="K1551" s="55" t="s">
         <v>265</v>
       </c>
     </row>
@@ -52128,13 +52286,13 @@
       <c r="B1552" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="C1552" s="55">
+      <c r="C1552" s="54">
         <v>46293</v>
       </c>
       <c r="D1552" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="E1552" s="52" t="s">
+      <c r="E1552" s="51" t="s">
         <v>579</v>
       </c>
       <c r="F1552" s="7">
@@ -52163,7 +52321,7 @@
       <c r="B1553" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1553" s="54">
+      <c r="C1553" s="53">
         <v>46294</v>
       </c>
       <c r="D1553" s="19" t="s">
@@ -52198,13 +52356,13 @@
       <c r="B1554" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C1554" s="55">
+      <c r="C1554" s="54">
         <v>46294</v>
       </c>
       <c r="D1554" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="E1554" s="52" t="s">
+      <c r="E1554" s="51" t="s">
         <v>18</v>
       </c>
       <c r="F1554" s="7">
@@ -52227,19 +52385,19 @@
       </c>
     </row>
     <row r="1555" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1555" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1555" s="56" t="s">
+      <c r="A1555" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1555" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="C1555" s="54">
+      <c r="C1555" s="53">
         <v>46294</v>
       </c>
-      <c r="D1555" s="56" t="s">
+      <c r="D1555" s="55" t="s">
         <v>374</v>
       </c>
-      <c r="E1555" s="56" t="s">
+      <c r="E1555" s="55" t="s">
         <v>19</v>
       </c>
       <c r="F1555" s="31">
@@ -52248,7 +52406,7 @@
       <c r="G1555" s="31">
         <v>145560101</v>
       </c>
-      <c r="H1555" s="56" t="s">
+      <c r="H1555" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1555" s="31" t="s">
@@ -52268,7 +52426,7 @@
       <c r="B1556" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="C1556" s="55">
+      <c r="C1556" s="54">
         <v>46294</v>
       </c>
       <c r="D1556" s="33" t="s">
@@ -52303,7 +52461,7 @@
       <c r="B1557" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="C1557" s="54">
+      <c r="C1557" s="53">
         <v>46294</v>
       </c>
       <c r="D1557" s="33" t="s">
@@ -52332,19 +52490,19 @@
       </c>
     </row>
     <row r="1558" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1558" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1558" s="52" t="s">
+      <c r="A1558" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1558" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1558" s="55">
+      <c r="C1558" s="54">
         <v>46294</v>
       </c>
-      <c r="D1558" s="52" t="s">
+      <c r="D1558" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="E1558" s="52" t="s">
+      <c r="E1558" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F1558" s="7">
@@ -52353,7 +52511,7 @@
       <c r="G1558" s="7">
         <v>145565082</v>
       </c>
-      <c r="H1558" s="52" t="s">
+      <c r="H1558" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1558" s="7" t="s">
@@ -52365,19 +52523,19 @@
       <c r="K1558" s="44"/>
     </row>
     <row r="1559" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1559" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1559" s="56" t="s">
+      <c r="A1559" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1559" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="C1559" s="54">
+      <c r="C1559" s="53">
         <v>46294</v>
       </c>
-      <c r="D1559" s="56" t="s">
+      <c r="D1559" s="55" t="s">
         <v>374</v>
       </c>
-      <c r="E1559" s="56" t="s">
+      <c r="E1559" s="55" t="s">
         <v>134</v>
       </c>
       <c r="F1559" s="31">
@@ -52386,33 +52544,33 @@
       <c r="G1559" s="31">
         <v>146591304</v>
       </c>
-      <c r="H1559" s="56" t="s">
+      <c r="H1559" s="55" t="s">
         <v>96</v>
       </c>
-      <c r="I1559" s="56" t="s">
+      <c r="I1559" s="55" t="s">
         <v>631</v>
       </c>
       <c r="J1559" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K1559" s="56" t="s">
+      <c r="K1559" s="55" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="1560" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1560" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1560" s="52" t="s">
+      <c r="A1560" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1560" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="C1560" s="55">
+      <c r="C1560" s="54">
         <v>46294</v>
       </c>
-      <c r="D1560" s="52" t="s">
+      <c r="D1560" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="E1560" s="52" t="s">
+      <c r="E1560" s="51" t="s">
         <v>311</v>
       </c>
       <c r="F1560" s="7">
@@ -52421,7 +52579,7 @@
       <c r="G1560" s="7">
         <v>146591034</v>
       </c>
-      <c r="H1560" s="52" t="s">
+      <c r="H1560" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1560" s="7" t="s">
@@ -52441,7 +52599,7 @@
       <c r="B1561" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C1561" s="54">
+      <c r="C1561" s="53">
         <v>46294</v>
       </c>
       <c r="D1561" s="19" t="s">
@@ -52470,19 +52628,19 @@
       </c>
     </row>
     <row r="1562" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1562" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1562" s="52" t="s">
+      <c r="A1562" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1562" s="51" t="s">
         <v>334</v>
       </c>
-      <c r="C1562" s="55">
+      <c r="C1562" s="54">
         <v>46294</v>
       </c>
-      <c r="D1562" s="52" t="s">
+      <c r="D1562" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="E1562" s="52" t="s">
+      <c r="E1562" s="51" t="s">
         <v>335</v>
       </c>
       <c r="F1562" s="7">
@@ -52491,7 +52649,7 @@
       <c r="G1562" s="7">
         <v>400915588</v>
       </c>
-      <c r="H1562" s="52" t="s">
+      <c r="H1562" s="51" t="s">
         <v>222</v>
       </c>
       <c r="I1562" s="44"/>
@@ -52501,19 +52659,19 @@
       <c r="K1562" s="44"/>
     </row>
     <row r="1563" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1563" s="56" t="s">
+      <c r="A1563" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B1563" s="56" t="s">
+      <c r="B1563" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="C1563" s="54">
+      <c r="C1563" s="53">
         <v>46294</v>
       </c>
-      <c r="D1563" s="56" t="s">
+      <c r="D1563" s="55" t="s">
         <v>374</v>
       </c>
-      <c r="E1563" s="56" t="s">
+      <c r="E1563" s="55" t="s">
         <v>23</v>
       </c>
       <c r="F1563" s="31" t="s">
@@ -52522,10 +52680,10 @@
       <c r="G1563" s="31" t="s">
         <v>632</v>
       </c>
-      <c r="H1563" s="56" t="s">
+      <c r="H1563" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="I1563" s="57"/>
+      <c r="I1563" s="56"/>
       <c r="J1563" s="9" t="s">
         <v>16</v>
       </c>
@@ -52540,13 +52698,13 @@
       <c r="B1564" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="C1564" s="55">
+      <c r="C1564" s="54">
         <v>46294</v>
       </c>
       <c r="D1564" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="E1564" s="52" t="s">
+      <c r="E1564" s="51" t="s">
         <v>310</v>
       </c>
       <c r="F1564" s="7" t="s">
@@ -52573,13 +52731,13 @@
       <c r="B1565" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="C1565" s="54">
+      <c r="C1565" s="53">
         <v>46294</v>
       </c>
       <c r="D1565" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="E1565" s="56" t="s">
+      <c r="E1565" s="55" t="s">
         <v>219</v>
       </c>
       <c r="F1565" s="31">
@@ -52608,7 +52766,7 @@
       <c r="B1566" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C1566" s="55">
+      <c r="C1566" s="54">
         <v>46294</v>
       </c>
       <c r="D1566" s="19" t="s">
@@ -52643,13 +52801,13 @@
       <c r="B1567" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C1567" s="54">
+      <c r="C1567" s="53">
         <v>46294</v>
       </c>
       <c r="D1567" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="E1567" s="56" t="s">
+      <c r="E1567" s="55" t="s">
         <v>29</v>
       </c>
       <c r="F1567" s="31">
@@ -52678,7 +52836,7 @@
       <c r="B1568" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="C1568" s="55">
+      <c r="C1568" s="54">
         <v>46294</v>
       </c>
       <c r="D1568" s="19" t="s">
@@ -52711,7 +52869,7 @@
       <c r="B1569" s="19" t="s">
         <v>578</v>
       </c>
-      <c r="C1569" s="54">
+      <c r="C1569" s="53">
         <v>46294</v>
       </c>
       <c r="D1569" s="19" t="s">
@@ -52738,19 +52896,19 @@
       <c r="K1569" s="34"/>
     </row>
     <row r="1570" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1570" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1570" s="52" t="s">
+      <c r="A1570" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1570" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="C1570" s="55">
+      <c r="C1570" s="54">
         <v>46295</v>
       </c>
-      <c r="D1570" s="52" t="s">
+      <c r="D1570" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="E1570" s="52" t="s">
+      <c r="E1570" s="51" t="s">
         <v>510</v>
       </c>
       <c r="F1570" s="7">
@@ -52759,16 +52917,16 @@
       <c r="G1570" s="7">
         <v>145560403</v>
       </c>
-      <c r="H1570" s="52" t="s">
+      <c r="H1570" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="I1570" s="52" t="s">
+      <c r="I1570" s="51" t="s">
         <v>635</v>
       </c>
       <c r="J1570" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K1570" s="52" t="s">
+      <c r="K1570" s="51" t="s">
         <v>236</v>
       </c>
     </row>
@@ -52779,13 +52937,13 @@
       <c r="B1571" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C1571" s="54">
+      <c r="C1571" s="53">
         <v>46295</v>
       </c>
       <c r="D1571" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="E1571" s="56" t="s">
+      <c r="E1571" s="55" t="s">
         <v>18</v>
       </c>
       <c r="F1571" s="31">
@@ -52808,19 +52966,19 @@
       </c>
     </row>
     <row r="1572" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1572" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1572" s="52" t="s">
+      <c r="A1572" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1572" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="C1572" s="55">
+      <c r="C1572" s="54">
         <v>46295</v>
       </c>
-      <c r="D1572" s="52" t="s">
+      <c r="D1572" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="E1572" s="52" t="s">
+      <c r="E1572" s="51" t="s">
         <v>19</v>
       </c>
       <c r="F1572" s="7">
@@ -52829,7 +52987,7 @@
       <c r="G1572" s="7">
         <v>145560833</v>
       </c>
-      <c r="H1572" s="52" t="s">
+      <c r="H1572" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1572" s="7" t="s">
@@ -52843,19 +53001,19 @@
       </c>
     </row>
     <row r="1573" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1573" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1573" s="56" t="s">
+      <c r="A1573" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1573" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1573" s="54">
+      <c r="C1573" s="53">
         <v>46295</v>
       </c>
-      <c r="D1573" s="56" t="s">
+      <c r="D1573" s="55" t="s">
         <v>374</v>
       </c>
-      <c r="E1573" s="56" t="s">
+      <c r="E1573" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1573" s="7">
@@ -52864,7 +53022,7 @@
       <c r="G1573" s="7">
         <v>145560403</v>
       </c>
-      <c r="H1573" s="56" t="s">
+      <c r="H1573" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1573" s="31" t="s">
@@ -52884,7 +53042,7 @@
       <c r="B1574" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C1574" s="55">
+      <c r="C1574" s="54">
         <v>46295</v>
       </c>
       <c r="D1574" s="29" t="s">
@@ -52913,19 +53071,19 @@
       </c>
     </row>
     <row r="1575" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1575" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1575" s="56" t="s">
+      <c r="A1575" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1575" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="C1575" s="54">
+      <c r="C1575" s="53">
         <v>46295</v>
       </c>
-      <c r="D1575" s="56" t="s">
+      <c r="D1575" s="55" t="s">
         <v>374</v>
       </c>
-      <c r="E1575" s="56" t="s">
+      <c r="E1575" s="55" t="s">
         <v>311</v>
       </c>
       <c r="F1575" s="31">
@@ -52934,7 +53092,7 @@
       <c r="G1575" s="31">
         <v>145564448</v>
       </c>
-      <c r="H1575" s="56" t="s">
+      <c r="H1575" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1575" s="31" t="s">
@@ -52948,19 +53106,19 @@
       </c>
     </row>
     <row r="1576" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1576" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1576" s="52" t="s">
+      <c r="A1576" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1576" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C1576" s="55">
+      <c r="C1576" s="54">
         <v>46295</v>
       </c>
-      <c r="D1576" s="52" t="s">
+      <c r="D1576" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="E1576" s="52" t="s">
+      <c r="E1576" s="51" t="s">
         <v>25</v>
       </c>
       <c r="F1576" s="7">
@@ -52969,7 +53127,7 @@
       <c r="G1576" s="7">
         <v>145565240</v>
       </c>
-      <c r="H1576" s="52" t="s">
+      <c r="H1576" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1576" s="7" t="s">
@@ -52989,7 +53147,7 @@
       <c r="B1577" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="C1577" s="54">
+      <c r="C1577" s="53">
         <v>46295</v>
       </c>
       <c r="D1577" s="19" t="s">
@@ -53016,19 +53174,19 @@
       <c r="K1577" s="34"/>
     </row>
     <row r="1578" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1578" s="52" t="s">
+      <c r="A1578" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B1578" s="52" t="s">
+      <c r="B1578" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="C1578" s="55">
+      <c r="C1578" s="54">
         <v>46295</v>
       </c>
-      <c r="D1578" s="52" t="s">
+      <c r="D1578" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="E1578" s="52" t="s">
+      <c r="E1578" s="51" t="s">
         <v>23</v>
       </c>
       <c r="F1578" s="7" t="s">
@@ -53037,7 +53195,7 @@
       <c r="G1578" s="7" t="s">
         <v>640</v>
       </c>
-      <c r="H1578" s="52" t="s">
+      <c r="H1578" s="51" t="s">
         <v>222</v>
       </c>
       <c r="I1578" s="7" t="s">
@@ -53057,13 +53215,13 @@
       <c r="B1579" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="C1579" s="54">
+      <c r="C1579" s="53">
         <v>46295</v>
       </c>
       <c r="D1579" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="E1579" s="56" t="s">
+      <c r="E1579" s="55" t="s">
         <v>310</v>
       </c>
       <c r="F1579" s="31" t="s">
@@ -53092,7 +53250,7 @@
       <c r="B1580" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="C1580" s="55">
+      <c r="C1580" s="54">
         <v>46295</v>
       </c>
       <c r="D1580" s="19" t="s">
@@ -53125,16 +53283,16 @@
       <c r="B1581" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C1581" s="54">
+      <c r="C1581" s="53">
         <v>46295</v>
       </c>
       <c r="D1581" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="E1581" s="56" t="s">
+      <c r="E1581" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="F1581" s="31" t="s">
+      <c r="F1581" s="9" t="s">
         <v>215</v>
       </c>
       <c r="G1581" s="31" t="s">
@@ -53146,7 +53304,9 @@
       <c r="I1581" s="31" t="s">
         <v>644</v>
       </c>
-      <c r="J1581" s="8"/>
+      <c r="J1581" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1581" s="31" t="s">
         <v>254</v>
       </c>
@@ -53158,7 +53318,7 @@
       <c r="B1582" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="C1582" s="55">
+      <c r="C1582" s="54">
         <v>46295</v>
       </c>
       <c r="D1582" s="19" t="s">
@@ -53191,7 +53351,7 @@
       <c r="B1583" s="19" t="s">
         <v>578</v>
       </c>
-      <c r="C1583" s="54">
+      <c r="C1583" s="53">
         <v>46295</v>
       </c>
       <c r="D1583" s="19" t="s">
@@ -53224,7 +53384,7 @@
       <c r="B1584" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C1584" s="55">
+      <c r="C1584" s="54">
         <v>46296</v>
       </c>
       <c r="D1584" s="33" t="s">
@@ -53253,19 +53413,19 @@
       </c>
     </row>
     <row r="1585" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1585" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1585" s="56" t="s">
+      <c r="A1585" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1585" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="C1585" s="54">
+      <c r="C1585" s="53">
         <v>46296</v>
       </c>
-      <c r="D1585" s="56" t="s">
+      <c r="D1585" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1585" s="56" t="s">
+      <c r="E1585" s="55" t="s">
         <v>510</v>
       </c>
       <c r="F1585" s="31">
@@ -53274,16 +53434,16 @@
       <c r="G1585" s="31">
         <v>146597758</v>
       </c>
-      <c r="H1585" s="56" t="s">
+      <c r="H1585" s="55" t="s">
         <v>96</v>
       </c>
-      <c r="I1585" s="56" t="s">
+      <c r="I1585" s="55" t="s">
         <v>592</v>
       </c>
       <c r="J1585" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K1585" s="56" t="s">
+      <c r="K1585" s="55" t="s">
         <v>371</v>
       </c>
     </row>
@@ -53294,7 +53454,7 @@
       <c r="B1586" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="C1586" s="55">
+      <c r="C1586" s="54">
         <v>46296</v>
       </c>
       <c r="D1586" s="33" t="s">
@@ -53329,7 +53489,7 @@
       <c r="B1587" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C1587" s="54">
+      <c r="C1587" s="53">
         <v>46296</v>
       </c>
       <c r="D1587" s="33" t="s">
@@ -53364,7 +53524,7 @@
       <c r="B1588" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="C1588" s="55">
+      <c r="C1588" s="54">
         <v>46296</v>
       </c>
       <c r="D1588" s="33" t="s">
@@ -53393,19 +53553,19 @@
       </c>
     </row>
     <row r="1589" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1589" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1589" s="56" t="s">
+      <c r="A1589" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1589" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1589" s="54">
+      <c r="C1589" s="53">
         <v>46296</v>
       </c>
-      <c r="D1589" s="56" t="s">
+      <c r="D1589" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1589" s="56" t="s">
+      <c r="E1589" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1589" s="31">
@@ -53414,7 +53574,7 @@
       <c r="G1589" s="31">
         <v>146597758</v>
       </c>
-      <c r="H1589" s="56" t="s">
+      <c r="H1589" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1589" s="31" t="s">
@@ -53434,7 +53594,7 @@
       <c r="B1590" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C1590" s="55">
+      <c r="C1590" s="54">
         <v>46296</v>
       </c>
       <c r="D1590" s="29" t="s">
@@ -53458,7 +53618,7 @@
       <c r="J1590" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="K1590" s="58"/>
+      <c r="K1590" s="57"/>
     </row>
     <row r="1591" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A1591" s="33" t="s">
@@ -53467,7 +53627,7 @@
       <c r="B1591" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C1591" s="54">
+      <c r="C1591" s="53">
         <v>46296</v>
       </c>
       <c r="D1591" s="33" t="s">
@@ -53496,19 +53656,19 @@
       </c>
     </row>
     <row r="1592" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1592" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1592" s="52" t="s">
+      <c r="A1592" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1592" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C1592" s="55">
+      <c r="C1592" s="54">
         <v>46296</v>
       </c>
-      <c r="D1592" s="52" t="s">
+      <c r="D1592" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1592" s="52" t="s">
+      <c r="E1592" s="51" t="s">
         <v>25</v>
       </c>
       <c r="F1592" s="7">
@@ -53517,7 +53677,7 @@
       <c r="G1592" s="7">
         <v>146595433</v>
       </c>
-      <c r="H1592" s="52" t="s">
+      <c r="H1592" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1592" s="7" t="s">
@@ -53537,7 +53697,7 @@
       <c r="B1593" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="C1593" s="54">
+      <c r="C1593" s="53">
         <v>46296</v>
       </c>
       <c r="D1593" s="19" t="s">
@@ -53566,19 +53726,19 @@
       </c>
     </row>
     <row r="1594" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1594" s="52" t="s">
+      <c r="A1594" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B1594" s="52" t="s">
+      <c r="B1594" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="C1594" s="55">
+      <c r="C1594" s="54">
         <v>46296</v>
       </c>
-      <c r="D1594" s="52" t="s">
+      <c r="D1594" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1594" s="52" t="s">
+      <c r="E1594" s="51" t="s">
         <v>23</v>
       </c>
       <c r="F1594" s="7" t="s">
@@ -53587,7 +53747,7 @@
       <c r="G1594" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="H1594" s="52" t="s">
+      <c r="H1594" s="51" t="s">
         <v>222</v>
       </c>
       <c r="I1594" s="7" t="s">
@@ -53607,13 +53767,13 @@
       <c r="B1595" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="C1595" s="54">
+      <c r="C1595" s="53">
         <v>46296</v>
       </c>
-      <c r="D1595" s="56" t="s">
+      <c r="D1595" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1595" s="56" t="s">
+      <c r="E1595" s="55" t="s">
         <v>310</v>
       </c>
       <c r="F1595" s="31" t="s">
@@ -53642,7 +53802,7 @@
       <c r="B1596" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="C1596" s="55">
+      <c r="C1596" s="54">
         <v>46296</v>
       </c>
       <c r="D1596" s="19" t="s">
@@ -53677,13 +53837,13 @@
       <c r="B1597" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C1597" s="54">
+      <c r="C1597" s="53">
         <v>46296</v>
       </c>
-      <c r="D1597" s="56" t="s">
+      <c r="D1597" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1597" s="56" t="s">
+      <c r="E1597" s="55" t="s">
         <v>29</v>
       </c>
       <c r="F1597" s="9" t="s">
@@ -53698,7 +53858,9 @@
       <c r="I1597" s="31" t="s">
         <v>658</v>
       </c>
-      <c r="J1597" s="8"/>
+      <c r="J1597" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1597" s="31" t="s">
         <v>254</v>
       </c>
@@ -53710,7 +53872,7 @@
       <c r="B1598" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="C1598" s="55">
+      <c r="C1598" s="54">
         <v>46296</v>
       </c>
       <c r="D1598" s="19" t="s">
@@ -53745,7 +53907,7 @@
       <c r="B1599" s="19" t="s">
         <v>578</v>
       </c>
-      <c r="C1599" s="54">
+      <c r="C1599" s="53">
         <v>46296</v>
       </c>
       <c r="D1599" s="19" t="s">
@@ -53774,19 +53936,19 @@
       </c>
     </row>
     <row r="1600" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1600" s="59"/>
-      <c r="B1600" s="59"/>
-      <c r="C1600" s="59"/>
-      <c r="D1600" s="52" t="s">
+      <c r="A1600" s="58"/>
+      <c r="B1600" s="58"/>
+      <c r="C1600" s="58"/>
+      <c r="D1600" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1600" s="59"/>
-      <c r="F1600" s="59"/>
-      <c r="G1600" s="59"/>
-      <c r="H1600" s="59"/>
-      <c r="I1600" s="59"/>
+      <c r="E1600" s="58"/>
+      <c r="F1600" s="58"/>
+      <c r="G1600" s="58"/>
+      <c r="H1600" s="58"/>
+      <c r="I1600" s="58"/>
       <c r="J1600" s="3"/>
-      <c r="K1600" s="59"/>
+      <c r="K1600" s="58"/>
     </row>
     <row r="1601" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1601" s="19" t="s">
@@ -53795,7 +53957,7 @@
       <c r="B1601" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1601" s="54">
+      <c r="C1601" s="53">
         <v>46297</v>
       </c>
       <c r="D1601" s="19" t="s">
@@ -53830,13 +53992,13 @@
       <c r="B1602" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C1602" s="55">
+      <c r="C1602" s="54">
         <v>46297</v>
       </c>
-      <c r="D1602" s="52" t="s">
+      <c r="D1602" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1602" s="52" t="s">
+      <c r="E1602" s="51" t="s">
         <v>18</v>
       </c>
       <c r="F1602" s="7">
@@ -53859,16 +54021,16 @@
       </c>
     </row>
     <row r="1603" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1603" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1603" s="56" t="s">
+      <c r="A1603" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1603" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="C1603" s="54">
+      <c r="C1603" s="53">
         <v>46297</v>
       </c>
-      <c r="D1603" s="56" t="s">
+      <c r="D1603" s="55" t="s">
         <v>645</v>
       </c>
       <c r="E1603" s="31" t="s">
@@ -53880,7 +54042,7 @@
       <c r="G1603" s="31">
         <v>146596225</v>
       </c>
-      <c r="H1603" s="56" t="s">
+      <c r="H1603" s="55" t="s">
         <v>222</v>
       </c>
       <c r="I1603" s="31" t="s">
@@ -53900,7 +54062,7 @@
       <c r="B1604" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C1604" s="55">
+      <c r="C1604" s="54">
         <v>46297</v>
       </c>
       <c r="D1604" s="33" t="s">
@@ -53929,19 +54091,19 @@
       </c>
     </row>
     <row r="1605" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1605" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1605" s="56" t="s">
+      <c r="A1605" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1605" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1605" s="54">
+      <c r="C1605" s="53">
         <v>46297</v>
       </c>
-      <c r="D1605" s="56" t="s">
+      <c r="D1605" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1605" s="56" t="s">
+      <c r="E1605" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1605" s="31">
@@ -53950,7 +54112,7 @@
       <c r="G1605" s="31">
         <v>146599648</v>
       </c>
-      <c r="H1605" s="56" t="s">
+      <c r="H1605" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1605" s="31" t="s">
@@ -53964,19 +54126,19 @@
       </c>
     </row>
     <row r="1606" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1606" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1606" s="52" t="s">
+      <c r="A1606" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1606" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1606" s="55">
+      <c r="C1606" s="54">
         <v>46297</v>
       </c>
-      <c r="D1606" s="52" t="s">
+      <c r="D1606" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1606" s="52" t="s">
+      <c r="E1606" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F1606" s="7">
@@ -53985,7 +54147,7 @@
       <c r="G1606" s="7">
         <v>146600063</v>
       </c>
-      <c r="H1606" s="52" t="s">
+      <c r="H1606" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1606" s="7" t="s">
@@ -53999,19 +54161,19 @@
       </c>
     </row>
     <row r="1607" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1607" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1607" s="56" t="s">
+      <c r="A1607" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1607" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1607" s="54">
+      <c r="C1607" s="53">
         <v>46297</v>
       </c>
-      <c r="D1607" s="56" t="s">
+      <c r="D1607" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1607" s="56" t="s">
+      <c r="E1607" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1607" s="31">
@@ -54020,7 +54182,7 @@
       <c r="G1607" s="31">
         <v>146600310</v>
       </c>
-      <c r="H1607" s="56" t="s">
+      <c r="H1607" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1607" s="31" t="s">
@@ -54034,19 +54196,19 @@
       </c>
     </row>
     <row r="1608" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1608" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1608" s="52" t="s">
+      <c r="A1608" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1608" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1608" s="55">
+      <c r="C1608" s="54">
         <v>46297</v>
       </c>
-      <c r="D1608" s="52" t="s">
+      <c r="D1608" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1608" s="52" t="s">
+      <c r="E1608" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F1608" s="7">
@@ -54055,7 +54217,7 @@
       <c r="G1608" s="7">
         <v>400939368</v>
       </c>
-      <c r="H1608" s="52" t="s">
+      <c r="H1608" s="51" t="s">
         <v>222</v>
       </c>
       <c r="I1608" s="7" t="s">
@@ -54075,7 +54237,7 @@
       <c r="B1609" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C1609" s="54">
+      <c r="C1609" s="53">
         <v>46297</v>
       </c>
       <c r="D1609" s="19" t="s">
@@ -54110,7 +54272,7 @@
       <c r="B1610" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C1610" s="55">
+      <c r="C1610" s="54">
         <v>46297</v>
       </c>
       <c r="D1610" s="29" t="s">
@@ -54134,7 +54296,7 @@
       <c r="J1610" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="K1610" s="58"/>
+      <c r="K1610" s="57"/>
     </row>
     <row r="1611" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1611" s="19" t="s">
@@ -54143,7 +54305,7 @@
       <c r="B1611" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C1611" s="54">
+      <c r="C1611" s="53">
         <v>46297</v>
       </c>
       <c r="D1611" s="19" t="s">
@@ -54178,7 +54340,7 @@
       <c r="B1612" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C1612" s="55">
+      <c r="C1612" s="54">
         <v>46297</v>
       </c>
       <c r="D1612" s="19" t="s">
@@ -54207,19 +54369,19 @@
       </c>
     </row>
     <row r="1613" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1613" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1613" s="56" t="s">
+      <c r="A1613" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1613" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="C1613" s="54">
+      <c r="C1613" s="53">
         <v>46297</v>
       </c>
-      <c r="D1613" s="56" t="s">
+      <c r="D1613" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1613" s="56" t="s">
+      <c r="E1613" s="55" t="s">
         <v>25</v>
       </c>
       <c r="F1613" s="7">
@@ -54228,7 +54390,7 @@
       <c r="G1613" s="7">
         <v>146597473</v>
       </c>
-      <c r="H1613" s="56" t="s">
+      <c r="H1613" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1613" s="9" t="s">
@@ -54248,7 +54410,7 @@
       <c r="B1614" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="C1614" s="55">
+      <c r="C1614" s="54">
         <v>46297</v>
       </c>
       <c r="D1614" s="19" t="s">
@@ -54277,19 +54439,19 @@
       </c>
     </row>
     <row r="1615" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1615" s="56" t="s">
+      <c r="A1615" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B1615" s="56" t="s">
+      <c r="B1615" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="C1615" s="54">
+      <c r="C1615" s="53">
         <v>46297</v>
       </c>
-      <c r="D1615" s="56" t="s">
+      <c r="D1615" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1615" s="56" t="s">
+      <c r="E1615" s="55" t="s">
         <v>23</v>
       </c>
       <c r="F1615" s="31" t="s">
@@ -54298,7 +54460,7 @@
       <c r="G1615" s="31" t="s">
         <v>662</v>
       </c>
-      <c r="H1615" s="56" t="s">
+      <c r="H1615" s="55" t="s">
         <v>222</v>
       </c>
       <c r="I1615" s="31" t="s">
@@ -54318,13 +54480,13 @@
       <c r="B1616" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="C1616" s="55">
+      <c r="C1616" s="54">
         <v>46297</v>
       </c>
-      <c r="D1616" s="52" t="s">
+      <c r="D1616" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1616" s="52" t="s">
+      <c r="E1616" s="51" t="s">
         <v>310</v>
       </c>
       <c r="F1616" s="7" t="s">
@@ -54353,7 +54515,7 @@
       <c r="B1617" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="C1617" s="54">
+      <c r="C1617" s="53">
         <v>46297</v>
       </c>
       <c r="D1617" s="19" t="s">
@@ -54388,13 +54550,13 @@
       <c r="B1618" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C1618" s="55">
+      <c r="C1618" s="54">
         <v>46297</v>
       </c>
-      <c r="D1618" s="52" t="s">
+      <c r="D1618" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1618" s="52" t="s">
+      <c r="E1618" s="51" t="s">
         <v>29</v>
       </c>
       <c r="F1618" s="4" t="s">
@@ -54409,7 +54571,9 @@
       <c r="I1618" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="J1618" s="3"/>
+      <c r="J1618" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1618" s="7" t="s">
         <v>254</v>
       </c>
@@ -54421,7 +54585,7 @@
       <c r="B1619" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="C1619" s="54">
+      <c r="C1619" s="53">
         <v>46297</v>
       </c>
       <c r="D1619" s="19" t="s">
@@ -54456,7 +54620,7 @@
       <c r="B1620" s="19" t="s">
         <v>578</v>
       </c>
-      <c r="C1620" s="55">
+      <c r="C1620" s="54">
         <v>46297</v>
       </c>
       <c r="D1620" s="19" t="s">
@@ -54491,7 +54655,7 @@
       <c r="B1621" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1621" s="54">
+      <c r="C1621" s="53">
         <v>46298</v>
       </c>
       <c r="D1621" s="19" t="s">
@@ -54526,7 +54690,7 @@
       <c r="B1622" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C1622" s="55">
+      <c r="C1622" s="54">
         <v>46298</v>
       </c>
       <c r="D1622" s="29" t="s">
@@ -54557,7 +54721,7 @@
       <c r="B1623" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C1623" s="54">
+      <c r="C1623" s="53">
         <v>46298</v>
       </c>
       <c r="D1623" s="29" t="s">
@@ -54582,19 +54746,19 @@
       <c r="K1623" s="16"/>
     </row>
     <row r="1624" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1624" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1624" s="52" t="s">
+      <c r="A1624" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1624" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1624" s="55">
+      <c r="C1624" s="54">
         <v>46298</v>
       </c>
-      <c r="D1624" s="52" t="s">
+      <c r="D1624" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1624" s="52" t="s">
+      <c r="E1624" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F1624" s="7">
@@ -54603,7 +54767,7 @@
       <c r="G1624" s="7">
         <v>146600392</v>
       </c>
-      <c r="H1624" s="52" t="s">
+      <c r="H1624" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1624" s="4" t="s">
@@ -54617,19 +54781,19 @@
       </c>
     </row>
     <row r="1625" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1625" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1625" s="56" t="s">
+      <c r="A1625" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1625" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1625" s="54">
+      <c r="C1625" s="53">
         <v>46298</v>
       </c>
-      <c r="D1625" s="56" t="s">
+      <c r="D1625" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1625" s="56" t="s">
+      <c r="E1625" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1625" s="31">
@@ -54638,7 +54802,7 @@
       <c r="G1625" s="31">
         <v>146600963</v>
       </c>
-      <c r="H1625" s="56" t="s">
+      <c r="H1625" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1625" s="9" t="s">
@@ -54652,19 +54816,19 @@
       </c>
     </row>
     <row r="1626" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1626" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1626" s="52" t="s">
+      <c r="A1626" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1626" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1626" s="55">
+      <c r="C1626" s="54">
         <v>46298</v>
       </c>
-      <c r="D1626" s="52" t="s">
+      <c r="D1626" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1626" s="52" t="s">
+      <c r="E1626" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F1626" s="7">
@@ -54673,7 +54837,7 @@
       <c r="G1626" s="7">
         <v>146600994</v>
       </c>
-      <c r="H1626" s="52" t="s">
+      <c r="H1626" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1626" s="4" t="s">
@@ -54693,7 +54857,7 @@
       <c r="B1627" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C1627" s="54">
+      <c r="C1627" s="53">
         <v>46298</v>
       </c>
       <c r="D1627" s="29" t="s">
@@ -54724,7 +54888,7 @@
       <c r="B1628" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="C1628" s="55">
+      <c r="C1628" s="54">
         <v>46298</v>
       </c>
       <c r="D1628" s="29" t="s">
@@ -54755,7 +54919,7 @@
       <c r="B1629" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C1629" s="54">
+      <c r="C1629" s="53">
         <v>46298</v>
       </c>
       <c r="D1629" s="19" t="s">
@@ -54790,7 +54954,7 @@
       <c r="B1630" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="C1630" s="55">
+      <c r="C1630" s="54">
         <v>46298</v>
       </c>
       <c r="D1630" s="19" t="s">
@@ -54819,19 +54983,19 @@
       </c>
     </row>
     <row r="1631" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1631" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1631" s="56" t="s">
+      <c r="A1631" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1631" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="C1631" s="54">
+      <c r="C1631" s="53">
         <v>46298</v>
       </c>
-      <c r="D1631" s="56" t="s">
+      <c r="D1631" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1631" s="56" t="s">
+      <c r="E1631" s="55" t="s">
         <v>23</v>
       </c>
       <c r="F1631" s="31">
@@ -54840,7 +55004,7 @@
       <c r="G1631" s="31">
         <v>146600308</v>
       </c>
-      <c r="H1631" s="56" t="s">
+      <c r="H1631" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1631" s="9" t="s">
@@ -54860,7 +55024,7 @@
       <c r="B1632" s="29" t="s">
         <v>309</v>
       </c>
-      <c r="C1632" s="55">
+      <c r="C1632" s="54">
         <v>46298</v>
       </c>
       <c r="D1632" s="29" t="s">
@@ -54891,7 +55055,7 @@
       <c r="B1633" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="C1633" s="54">
+      <c r="C1633" s="53">
         <v>46298</v>
       </c>
       <c r="D1633" s="29" t="s">
@@ -54922,7 +55086,7 @@
       <c r="B1634" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C1634" s="55">
+      <c r="C1634" s="54">
         <v>46298</v>
       </c>
       <c r="D1634" s="29" t="s">
@@ -54953,7 +55117,7 @@
       <c r="B1635" s="29" t="s">
         <v>501</v>
       </c>
-      <c r="C1635" s="54">
+      <c r="C1635" s="53">
         <v>46298</v>
       </c>
       <c r="D1635" s="29" t="s">
@@ -54984,7 +55148,7 @@
       <c r="B1636" s="29" t="s">
         <v>578</v>
       </c>
-      <c r="C1636" s="55">
+      <c r="C1636" s="54">
         <v>46298</v>
       </c>
       <c r="D1636" s="29" t="s">
@@ -55015,7 +55179,7 @@
       <c r="B1637" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C1637" s="54">
+      <c r="C1637" s="53">
         <v>46299</v>
       </c>
       <c r="D1637" s="29" t="s">
@@ -55046,7 +55210,7 @@
       <c r="B1638" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C1638" s="55">
+      <c r="C1638" s="54">
         <v>46299</v>
       </c>
       <c r="D1638" s="29" t="s">
@@ -55071,19 +55235,19 @@
       <c r="K1638" s="16"/>
     </row>
     <row r="1639" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1639" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1639" s="56" t="s">
+      <c r="A1639" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1639" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="C1639" s="54">
+      <c r="C1639" s="53">
         <v>46299</v>
       </c>
-      <c r="D1639" s="56" t="s">
+      <c r="D1639" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1639" s="56" t="s">
+      <c r="E1639" s="55" t="s">
         <v>19</v>
       </c>
       <c r="F1639" s="31">
@@ -55092,7 +55256,7 @@
       <c r="G1639" s="31">
         <v>146599953</v>
       </c>
-      <c r="H1639" s="56" t="s">
+      <c r="H1639" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1639" s="9" t="s">
@@ -55106,19 +55270,19 @@
       </c>
     </row>
     <row r="1640" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1640" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1640" s="52" t="s">
+      <c r="A1640" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1640" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1640" s="55">
+      <c r="C1640" s="54">
         <v>46299</v>
       </c>
-      <c r="D1640" s="52" t="s">
+      <c r="D1640" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1640" s="52" t="s">
+      <c r="E1640" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F1640" s="7">
@@ -55127,7 +55291,7 @@
       <c r="G1640" s="7">
         <v>146602185</v>
       </c>
-      <c r="H1640" s="52" t="s">
+      <c r="H1640" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1640" s="4" t="s">
@@ -55141,19 +55305,19 @@
       </c>
     </row>
     <row r="1641" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1641" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1641" s="56" t="s">
+      <c r="A1641" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1641" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1641" s="54">
+      <c r="C1641" s="53">
         <v>46299</v>
       </c>
-      <c r="D1641" s="56" t="s">
+      <c r="D1641" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1641" s="56" t="s">
+      <c r="E1641" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1641" s="31">
@@ -55162,7 +55326,7 @@
       <c r="G1641" s="31">
         <v>146601653</v>
       </c>
-      <c r="H1641" s="56" t="s">
+      <c r="H1641" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1641" s="9" t="s">
@@ -55182,7 +55346,7 @@
       <c r="B1642" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C1642" s="55">
+      <c r="C1642" s="54">
         <v>46299</v>
       </c>
       <c r="D1642" s="29" t="s">
@@ -55213,7 +55377,7 @@
       <c r="B1643" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="C1643" s="54">
+      <c r="C1643" s="53">
         <v>46299</v>
       </c>
       <c r="D1643" s="29" t="s">
@@ -55244,7 +55408,7 @@
       <c r="B1644" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C1644" s="55">
+      <c r="C1644" s="54">
         <v>46299</v>
       </c>
       <c r="D1644" s="29" t="s">
@@ -55275,7 +55439,7 @@
       <c r="B1645" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="C1645" s="54">
+      <c r="C1645" s="53">
         <v>46299</v>
       </c>
       <c r="D1645" s="19" t="s">
@@ -55310,7 +55474,7 @@
       <c r="B1646" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C1646" s="55">
+      <c r="C1646" s="54">
         <v>46299</v>
       </c>
       <c r="D1646" s="29" t="s">
@@ -55341,7 +55505,7 @@
       <c r="B1647" s="29" t="s">
         <v>309</v>
       </c>
-      <c r="C1647" s="54">
+      <c r="C1647" s="53">
         <v>46299</v>
       </c>
       <c r="D1647" s="29" t="s">
@@ -55372,7 +55536,7 @@
       <c r="B1648" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="C1648" s="55">
+      <c r="C1648" s="54">
         <v>46299</v>
       </c>
       <c r="D1648" s="29" t="s">
@@ -55403,7 +55567,7 @@
       <c r="B1649" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C1649" s="54">
+      <c r="C1649" s="53">
         <v>46299</v>
       </c>
       <c r="D1649" s="29" t="s">
@@ -55434,7 +55598,7 @@
       <c r="B1650" s="29" t="s">
         <v>501</v>
       </c>
-      <c r="C1650" s="55">
+      <c r="C1650" s="54">
         <v>46299</v>
       </c>
       <c r="D1650" s="29" t="s">
@@ -55465,7 +55629,7 @@
       <c r="B1651" s="29" t="s">
         <v>578</v>
       </c>
-      <c r="C1651" s="54">
+      <c r="C1651" s="53">
         <v>46299</v>
       </c>
       <c r="D1651" s="29" t="s">
@@ -55496,7 +55660,7 @@
       <c r="B1652" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1652" s="55">
+      <c r="C1652" s="54">
         <v>46300</v>
       </c>
       <c r="D1652" s="19" t="s">
@@ -55527,13 +55691,13 @@
       <c r="B1653" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C1653" s="54">
+      <c r="C1653" s="53">
         <v>46300</v>
       </c>
-      <c r="D1653" s="56" t="s">
+      <c r="D1653" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1653" s="56" t="s">
+      <c r="E1653" s="55" t="s">
         <v>18</v>
       </c>
       <c r="F1653" s="31">
@@ -55556,19 +55720,19 @@
       </c>
     </row>
     <row r="1654" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1654" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1654" s="52" t="s">
+      <c r="A1654" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1654" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="C1654" s="55">
+      <c r="C1654" s="54">
         <v>46300</v>
       </c>
-      <c r="D1654" s="52" t="s">
+      <c r="D1654" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1654" s="52" t="s">
+      <c r="E1654" s="51" t="s">
         <v>19</v>
       </c>
       <c r="F1654" s="7">
@@ -55577,7 +55741,7 @@
       <c r="G1654" s="7">
         <v>146600514</v>
       </c>
-      <c r="H1654" s="52" t="s">
+      <c r="H1654" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1654" s="4" t="s">
@@ -55591,19 +55755,19 @@
       </c>
     </row>
     <row r="1655" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1655" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1655" s="56" t="s">
+      <c r="A1655" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1655" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1655" s="54">
+      <c r="C1655" s="53">
         <v>46300</v>
       </c>
-      <c r="D1655" s="56" t="s">
+      <c r="D1655" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1655" s="56" t="s">
+      <c r="E1655" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1655" s="31">
@@ -55612,7 +55776,7 @@
       <c r="G1655" s="31">
         <v>146600989</v>
       </c>
-      <c r="H1655" s="56" t="s">
+      <c r="H1655" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1655" s="9" t="s">
@@ -55626,19 +55790,19 @@
       </c>
     </row>
     <row r="1656" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1656" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1656" s="52" t="s">
+      <c r="A1656" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1656" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1656" s="55">
+      <c r="C1656" s="54">
         <v>46300</v>
       </c>
-      <c r="D1656" s="52" t="s">
+      <c r="D1656" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1656" s="52" t="s">
+      <c r="E1656" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F1656" s="7">
@@ -55647,7 +55811,7 @@
       <c r="G1656" s="7">
         <v>146603593</v>
       </c>
-      <c r="H1656" s="52" t="s">
+      <c r="H1656" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1656" s="4" t="s">
@@ -55661,19 +55825,19 @@
       </c>
     </row>
     <row r="1657" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1657" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1657" s="56" t="s">
+      <c r="A1657" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1657" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1657" s="54">
+      <c r="C1657" s="53">
         <v>46300</v>
       </c>
-      <c r="D1657" s="56" t="s">
+      <c r="D1657" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1657" s="56" t="s">
+      <c r="E1657" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1657" s="31">
@@ -55682,7 +55846,7 @@
       <c r="G1657" s="31">
         <v>146604286</v>
       </c>
-      <c r="H1657" s="56" t="s">
+      <c r="H1657" s="55" t="s">
         <v>96</v>
       </c>
       <c r="I1657" s="9" t="s">
@@ -55696,19 +55860,19 @@
       </c>
     </row>
     <row r="1658" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1658" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1658" s="52" t="s">
+      <c r="A1658" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1658" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="C1658" s="55">
+      <c r="C1658" s="54">
         <v>46300</v>
       </c>
-      <c r="D1658" s="52" t="s">
+      <c r="D1658" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1658" s="52" t="s">
+      <c r="E1658" s="51" t="s">
         <v>134</v>
       </c>
       <c r="F1658" s="7">
@@ -55717,7 +55881,7 @@
       <c r="G1658" s="7">
         <v>146595782</v>
       </c>
-      <c r="H1658" s="52" t="s">
+      <c r="H1658" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1658" s="4" t="s">
@@ -55731,19 +55895,19 @@
       </c>
     </row>
     <row r="1659" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1659" s="56" t="s">
+      <c r="A1659" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="B1659" s="56" t="s">
+      <c r="B1659" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="C1659" s="54">
+      <c r="C1659" s="53">
         <v>46300</v>
       </c>
-      <c r="D1659" s="56" t="s">
+      <c r="D1659" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1659" s="56" t="s">
+      <c r="E1659" s="55" t="s">
         <v>311</v>
       </c>
       <c r="F1659" s="31">
@@ -55752,7 +55916,7 @@
       <c r="G1659" s="31" t="s">
         <v>670</v>
       </c>
-      <c r="H1659" s="56" t="s">
+      <c r="H1659" s="55" t="s">
         <v>222</v>
       </c>
       <c r="I1659" s="9" t="s">
@@ -55766,19 +55930,19 @@
       </c>
     </row>
     <row r="1660" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1660" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1660" s="52" t="s">
+      <c r="A1660" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1660" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C1660" s="55">
+      <c r="C1660" s="54">
         <v>46300</v>
       </c>
-      <c r="D1660" s="52" t="s">
+      <c r="D1660" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1660" s="52" t="s">
+      <c r="E1660" s="51" t="s">
         <v>25</v>
       </c>
       <c r="F1660" s="7">
@@ -55787,7 +55951,7 @@
       <c r="G1660" s="7">
         <v>146597473</v>
       </c>
-      <c r="H1660" s="52" t="s">
+      <c r="H1660" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I1660" s="4" t="s">
@@ -55807,7 +55971,7 @@
       <c r="B1661" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="C1661" s="54">
+      <c r="C1661" s="53">
         <v>46300</v>
       </c>
       <c r="D1661" s="29" t="s">
@@ -55834,19 +55998,19 @@
       <c r="K1661" s="16"/>
     </row>
     <row r="1662" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1662" s="52" t="s">
+      <c r="A1662" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B1662" s="52" t="s">
+      <c r="B1662" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="C1662" s="55">
+      <c r="C1662" s="54">
         <v>46300</v>
       </c>
-      <c r="D1662" s="52" t="s">
+      <c r="D1662" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1662" s="52" t="s">
+      <c r="E1662" s="51" t="s">
         <v>23</v>
       </c>
       <c r="F1662" s="7" t="s">
@@ -55855,7 +56019,7 @@
       <c r="G1662" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="H1662" s="52" t="s">
+      <c r="H1662" s="51" t="s">
         <v>222</v>
       </c>
       <c r="I1662" s="4" t="s">
@@ -55875,13 +56039,13 @@
       <c r="B1663" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="C1663" s="54">
+      <c r="C1663" s="53">
         <v>46300</v>
       </c>
-      <c r="D1663" s="56" t="s">
+      <c r="D1663" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1663" s="56" t="s">
+      <c r="E1663" s="55" t="s">
         <v>310</v>
       </c>
       <c r="F1663" s="31" t="s">
@@ -55910,13 +56074,13 @@
       <c r="B1664" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C1664" s="55">
+      <c r="C1664" s="54">
         <v>46300</v>
       </c>
-      <c r="D1664" s="52" t="s">
+      <c r="D1664" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1664" s="52" t="s">
+      <c r="E1664" s="51" t="s">
         <v>219</v>
       </c>
       <c r="F1664" s="7" t="s">
@@ -55945,7 +56109,7 @@
       <c r="B1665" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C1665" s="54">
+      <c r="C1665" s="53">
         <v>46300</v>
       </c>
       <c r="D1665" s="29" t="s">
@@ -55972,7 +56136,7 @@
       <c r="B1666" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="C1666" s="55">
+      <c r="C1666" s="54">
         <v>46300</v>
       </c>
       <c r="D1666" s="19" t="s">
@@ -55999,7 +56163,7 @@
       <c r="B1667" s="19" t="s">
         <v>578</v>
       </c>
-      <c r="C1667" s="54">
+      <c r="C1667" s="53">
         <v>46300</v>
       </c>
       <c r="D1667" s="19" t="s">
@@ -56026,7 +56190,7 @@
       <c r="B1668" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1668" s="55">
+      <c r="C1668" s="54">
         <v>46301</v>
       </c>
       <c r="D1668" s="19" t="s">
@@ -56053,13 +56217,13 @@
       <c r="B1669" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C1669" s="54">
+      <c r="C1669" s="53">
         <v>46301</v>
       </c>
-      <c r="D1669" s="56" t="s">
+      <c r="D1669" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1669" s="56" t="s">
+      <c r="E1669" s="55" t="s">
         <v>18</v>
       </c>
       <c r="F1669" s="31">
@@ -56082,19 +56246,19 @@
       </c>
     </row>
     <row r="1670" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1670" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1670" s="52" t="s">
+      <c r="A1670" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1670" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="C1670" s="55">
+      <c r="C1670" s="54">
         <v>46301</v>
       </c>
-      <c r="D1670" s="52" t="s">
+      <c r="D1670" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1670" s="52" t="s">
+      <c r="E1670" s="51" t="s">
         <v>19</v>
       </c>
       <c r="F1670" s="7">
@@ -56117,19 +56281,19 @@
       </c>
     </row>
     <row r="1671" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1671" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1671" s="56" t="s">
+      <c r="A1671" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1671" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1671" s="54">
+      <c r="C1671" s="53">
         <v>46301</v>
       </c>
-      <c r="D1671" s="56" t="s">
+      <c r="D1671" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1671" s="56" t="s">
+      <c r="E1671" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1671" s="31">
@@ -56152,19 +56316,19 @@
       </c>
     </row>
     <row r="1672" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1672" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1672" s="52" t="s">
+      <c r="A1672" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1672" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1672" s="55">
+      <c r="C1672" s="54">
         <v>46301</v>
       </c>
-      <c r="D1672" s="52" t="s">
+      <c r="D1672" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1672" s="52" t="s">
+      <c r="E1672" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F1672" s="7">
@@ -56187,19 +56351,19 @@
       </c>
     </row>
     <row r="1673" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1673" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1673" s="56" t="s">
+      <c r="A1673" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1673" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="C1673" s="54">
+      <c r="C1673" s="53">
         <v>46301</v>
       </c>
-      <c r="D1673" s="56" t="s">
+      <c r="D1673" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1673" s="56" t="s">
+      <c r="E1673" s="55" t="s">
         <v>134</v>
       </c>
       <c r="F1673" s="31">
@@ -56222,19 +56386,19 @@
       </c>
     </row>
     <row r="1674" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1674" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1674" s="52" t="s">
+      <c r="A1674" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1674" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="C1674" s="55">
+      <c r="C1674" s="54">
         <v>46301</v>
       </c>
-      <c r="D1674" s="52" t="s">
+      <c r="D1674" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1674" s="52" t="s">
+      <c r="E1674" s="51" t="s">
         <v>311</v>
       </c>
       <c r="F1674" s="7">
@@ -56263,7 +56427,7 @@
       <c r="B1675" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C1675" s="54">
+      <c r="C1675" s="53">
         <v>46301</v>
       </c>
       <c r="D1675" s="19" t="s">
@@ -56292,19 +56456,19 @@
       </c>
     </row>
     <row r="1676" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1676" s="52" t="s">
+      <c r="A1676" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="B1676" s="52" t="s">
+      <c r="B1676" s="51" t="s">
         <v>334</v>
       </c>
-      <c r="C1676" s="55">
+      <c r="C1676" s="54">
         <v>46301</v>
       </c>
-      <c r="D1676" s="52" t="s">
+      <c r="D1676" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1676" s="52" t="s">
+      <c r="E1676" s="51" t="s">
         <v>335</v>
       </c>
       <c r="F1676" s="4">
@@ -56325,19 +56489,19 @@
       <c r="K1676" s="3"/>
     </row>
     <row r="1677" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1677" s="56" t="s">
+      <c r="A1677" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B1677" s="56" t="s">
+      <c r="B1677" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="C1677" s="54">
+      <c r="C1677" s="53">
         <v>46301</v>
       </c>
-      <c r="D1677" s="56" t="s">
+      <c r="D1677" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1677" s="56" t="s">
+      <c r="E1677" s="55" t="s">
         <v>23</v>
       </c>
       <c r="F1677" s="31" t="s">
@@ -56366,13 +56530,13 @@
       <c r="B1678" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="C1678" s="55">
+      <c r="C1678" s="54">
         <v>46301</v>
       </c>
-      <c r="D1678" s="52" t="s">
+      <c r="D1678" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1678" s="52" t="s">
+      <c r="E1678" s="51" t="s">
         <v>310</v>
       </c>
       <c r="F1678" s="7" t="s">
@@ -56401,13 +56565,13 @@
       <c r="B1679" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="C1679" s="54">
+      <c r="C1679" s="53">
         <v>46301</v>
       </c>
-      <c r="D1679" s="56" t="s">
+      <c r="D1679" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1679" s="56" t="s">
+      <c r="E1679" s="55" t="s">
         <v>219</v>
       </c>
       <c r="F1679" s="31" t="s">
@@ -56436,13 +56600,13 @@
       <c r="B1680" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C1680" s="55">
+      <c r="C1680" s="54">
         <v>46301</v>
       </c>
-      <c r="D1680" s="52" t="s">
+      <c r="D1680" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1680" s="52" t="s">
+      <c r="E1680" s="51" t="s">
         <v>29</v>
       </c>
       <c r="F1680" s="4" t="s">
@@ -56471,7 +56635,7 @@
       <c r="B1681" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="C1681" s="54">
+      <c r="C1681" s="53">
         <v>46301</v>
       </c>
       <c r="D1681" s="19" t="s">
@@ -56498,7 +56662,7 @@
       <c r="B1682" s="19" t="s">
         <v>578</v>
       </c>
-      <c r="C1682" s="55">
+      <c r="C1682" s="54">
         <v>46301</v>
       </c>
       <c r="D1682" s="19" t="s">
@@ -56519,19 +56683,19 @@
       <c r="K1682" s="13"/>
     </row>
     <row r="1683" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1683" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1683" s="56" t="s">
+      <c r="A1683" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1683" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="C1683" s="54">
+      <c r="C1683" s="53">
         <v>46302</v>
       </c>
-      <c r="D1683" s="56" t="s">
+      <c r="D1683" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1683" s="56" t="s">
+      <c r="E1683" s="55" t="s">
         <v>510</v>
       </c>
       <c r="F1683" s="9">
@@ -56560,13 +56724,13 @@
       <c r="B1684" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C1684" s="55">
+      <c r="C1684" s="54">
         <v>46302</v>
       </c>
-      <c r="D1684" s="52" t="s">
+      <c r="D1684" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1684" s="52" t="s">
+      <c r="E1684" s="51" t="s">
         <v>18</v>
       </c>
       <c r="F1684" s="7">
@@ -56589,19 +56753,19 @@
       </c>
     </row>
     <row r="1685" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1685" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1685" s="56" t="s">
+      <c r="A1685" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1685" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="C1685" s="54">
+      <c r="C1685" s="53">
         <v>46302</v>
       </c>
-      <c r="D1685" s="56" t="s">
+      <c r="D1685" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1685" s="56" t="s">
+      <c r="E1685" s="55" t="s">
         <v>19</v>
       </c>
       <c r="F1685" s="9">
@@ -56624,19 +56788,19 @@
       </c>
     </row>
     <row r="1686" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1686" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1686" s="52" t="s">
+      <c r="A1686" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1686" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1686" s="55">
+      <c r="C1686" s="54">
         <v>46302</v>
       </c>
-      <c r="D1686" s="52" t="s">
+      <c r="D1686" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1686" s="52" t="s">
+      <c r="E1686" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F1686" s="7">
@@ -56659,19 +56823,19 @@
       </c>
     </row>
     <row r="1687" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1687" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1687" s="56" t="s">
+      <c r="A1687" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1687" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1687" s="54">
+      <c r="C1687" s="53">
         <v>46302</v>
       </c>
-      <c r="D1687" s="56" t="s">
+      <c r="D1687" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1687" s="56" t="s">
+      <c r="E1687" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1687" s="7">
@@ -56700,7 +56864,7 @@
       <c r="B1688" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C1688" s="55">
+      <c r="C1688" s="54">
         <v>46302</v>
       </c>
       <c r="D1688" s="19" t="s">
@@ -56721,19 +56885,19 @@
       <c r="K1688" s="13"/>
     </row>
     <row r="1689" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1689" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1689" s="56" t="s">
+      <c r="A1689" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1689" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="C1689" s="54">
+      <c r="C1689" s="53">
         <v>46302</v>
       </c>
-      <c r="D1689" s="56" t="s">
+      <c r="D1689" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1689" s="56" t="s">
+      <c r="E1689" s="55" t="s">
         <v>311</v>
       </c>
       <c r="F1689" s="31">
@@ -56762,7 +56926,7 @@
       <c r="B1690" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C1690" s="55">
+      <c r="C1690" s="54">
         <v>46302</v>
       </c>
       <c r="D1690" s="19" t="s">
@@ -56797,7 +56961,7 @@
       <c r="B1691" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="C1691" s="54">
+      <c r="C1691" s="53">
         <v>46302</v>
       </c>
       <c r="D1691" s="19" t="s">
@@ -56820,19 +56984,19 @@
       </c>
     </row>
     <row r="1692" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1692" s="52" t="s">
+      <c r="A1692" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B1692" s="52" t="s">
+      <c r="B1692" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="C1692" s="55">
+      <c r="C1692" s="54">
         <v>46302</v>
       </c>
-      <c r="D1692" s="52" t="s">
+      <c r="D1692" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1692" s="52" t="s">
+      <c r="E1692" s="51" t="s">
         <v>23</v>
       </c>
       <c r="F1692" s="4" t="s">
@@ -56861,13 +57025,13 @@
       <c r="B1693" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="C1693" s="54">
+      <c r="C1693" s="53">
         <v>46302</v>
       </c>
-      <c r="D1693" s="56" t="s">
+      <c r="D1693" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1693" s="56" t="s">
+      <c r="E1693" s="55" t="s">
         <v>310</v>
       </c>
       <c r="F1693" s="9" t="s">
@@ -56896,13 +57060,13 @@
       <c r="B1694" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C1694" s="55">
+      <c r="C1694" s="54">
         <v>46302</v>
       </c>
-      <c r="D1694" s="52" t="s">
+      <c r="D1694" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1694" s="52" t="s">
+      <c r="E1694" s="51" t="s">
         <v>219</v>
       </c>
       <c r="F1694" s="4" t="s">
@@ -56931,13 +57095,13 @@
       <c r="B1695" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C1695" s="54">
+      <c r="C1695" s="53">
         <v>46302</v>
       </c>
-      <c r="D1695" s="56" t="s">
+      <c r="D1695" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1695" s="56" t="s">
+      <c r="E1695" s="55" t="s">
         <v>29</v>
       </c>
       <c r="F1695" s="9" t="s">
@@ -56960,19 +57124,19 @@
       </c>
     </row>
     <row r="1696" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A1696" s="52" t="s">
+      <c r="A1696" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B1696" s="52" t="s">
+      <c r="B1696" s="51" t="s">
         <v>501</v>
       </c>
-      <c r="C1696" s="55">
+      <c r="C1696" s="54">
         <v>46302</v>
       </c>
-      <c r="D1696" s="52" t="s">
+      <c r="D1696" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1696" s="52" t="s">
+      <c r="E1696" s="51" t="s">
         <v>13</v>
       </c>
       <c r="F1696" s="4" t="s">
@@ -57001,13 +57165,13 @@
       <c r="B1697" s="31" t="s">
         <v>578</v>
       </c>
-      <c r="C1697" s="54">
+      <c r="C1697" s="53">
         <v>46302</v>
       </c>
-      <c r="D1697" s="56" t="s">
+      <c r="D1697" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1697" s="56" t="s">
+      <c r="E1697" s="55" t="s">
         <v>579</v>
       </c>
       <c r="F1697" s="9" t="s">
@@ -57036,7 +57200,7 @@
       <c r="B1698" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1698" s="55">
+      <c r="C1698" s="54">
         <v>46303</v>
       </c>
       <c r="D1698" s="19" t="s">
@@ -57065,13 +57229,13 @@
       <c r="B1699" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C1699" s="54">
+      <c r="C1699" s="53">
         <v>46303</v>
       </c>
-      <c r="D1699" s="56" t="s">
+      <c r="D1699" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1699" s="56" t="s">
+      <c r="E1699" s="55" t="s">
         <v>18</v>
       </c>
       <c r="F1699" s="7">
@@ -57094,19 +57258,19 @@
       </c>
     </row>
     <row r="1700" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1700" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1700" s="52" t="s">
+      <c r="A1700" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1700" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="C1700" s="55">
+      <c r="C1700" s="54">
         <v>46303</v>
       </c>
-      <c r="D1700" s="52" t="s">
+      <c r="D1700" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1700" s="52" t="s">
+      <c r="E1700" s="51" t="s">
         <v>19</v>
       </c>
       <c r="F1700" s="7">
@@ -57129,19 +57293,19 @@
       </c>
     </row>
     <row r="1701" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1701" s="56" t="s">
+      <c r="A1701" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B1701" s="56" t="s">
+      <c r="B1701" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1701" s="54">
+      <c r="C1701" s="53">
         <v>46303</v>
       </c>
-      <c r="D1701" s="56" t="s">
+      <c r="D1701" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1701" s="56" t="s">
+      <c r="E1701" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1701" s="9" t="s">
@@ -57170,7 +57334,7 @@
       <c r="B1702" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C1702" s="55">
+      <c r="C1702" s="54">
         <v>46303</v>
       </c>
       <c r="D1702" s="19" t="s">
@@ -57193,19 +57357,19 @@
       </c>
     </row>
     <row r="1703" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1703" s="56" t="s">
+      <c r="A1703" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="B1703" s="56" t="s">
+      <c r="B1703" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="C1703" s="54">
+      <c r="C1703" s="53">
         <v>46303</v>
       </c>
-      <c r="D1703" s="56" t="s">
+      <c r="D1703" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1703" s="56" t="s">
+      <c r="E1703" s="55" t="s">
         <v>311</v>
       </c>
       <c r="F1703" s="9">
@@ -57228,19 +57392,19 @@
       </c>
     </row>
     <row r="1704" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1704" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1704" s="52" t="s">
+      <c r="A1704" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1704" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C1704" s="55">
+      <c r="C1704" s="54">
         <v>46303</v>
       </c>
-      <c r="D1704" s="52" t="s">
+      <c r="D1704" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1704" s="52" t="s">
+      <c r="E1704" s="51" t="s">
         <v>25</v>
       </c>
       <c r="F1704" s="7">
@@ -57269,7 +57433,7 @@
       <c r="B1705" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="C1705" s="54">
+      <c r="C1705" s="53">
         <v>46303</v>
       </c>
       <c r="D1705" s="19" t="s">
@@ -57292,19 +57456,19 @@
       </c>
     </row>
     <row r="1706" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1706" s="52" t="s">
+      <c r="A1706" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B1706" s="52" t="s">
+      <c r="B1706" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="C1706" s="55">
+      <c r="C1706" s="54">
         <v>46303</v>
       </c>
-      <c r="D1706" s="52" t="s">
+      <c r="D1706" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1706" s="52" t="s">
+      <c r="E1706" s="51" t="s">
         <v>23</v>
       </c>
       <c r="F1706" s="4" t="s">
@@ -57333,13 +57497,13 @@
       <c r="B1707" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="C1707" s="54">
+      <c r="C1707" s="53">
         <v>46303</v>
       </c>
-      <c r="D1707" s="56" t="s">
+      <c r="D1707" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1707" s="56" t="s">
+      <c r="E1707" s="55" t="s">
         <v>310</v>
       </c>
       <c r="F1707" s="9" t="s">
@@ -57368,7 +57532,7 @@
       <c r="B1708" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="C1708" s="55">
+      <c r="C1708" s="54">
         <v>46303</v>
       </c>
       <c r="D1708" s="19" t="s">
@@ -57403,7 +57567,7 @@
       <c r="B1709" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C1709" s="54">
+      <c r="C1709" s="53">
         <v>46303</v>
       </c>
       <c r="D1709" s="19" t="s">
@@ -57438,13 +57602,13 @@
       <c r="B1710" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C1710" s="55">
+      <c r="C1710" s="54">
         <v>46303</v>
       </c>
-      <c r="D1710" s="52" t="s">
+      <c r="D1710" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1710" s="52" t="s">
+      <c r="E1710" s="51" t="s">
         <v>29</v>
       </c>
       <c r="F1710" s="7">
@@ -57459,7 +57623,9 @@
       <c r="I1710" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="J1710" s="3"/>
+      <c r="J1710" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1710" s="4" t="s">
         <v>286</v>
       </c>
@@ -57471,7 +57637,7 @@
       <c r="B1711" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="C1711" s="54">
+      <c r="C1711" s="53">
         <v>46303</v>
       </c>
       <c r="D1711" s="19" t="s">
@@ -57506,13 +57672,13 @@
       <c r="B1712" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="C1712" s="55">
+      <c r="C1712" s="54">
         <v>46303</v>
       </c>
-      <c r="D1712" s="52" t="s">
+      <c r="D1712" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1712" s="52" t="s">
+      <c r="E1712" s="51" t="s">
         <v>579</v>
       </c>
       <c r="F1712" s="4" t="s">
@@ -57541,7 +57707,7 @@
       <c r="B1713" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1713" s="54">
+      <c r="C1713" s="53">
         <v>46304</v>
       </c>
       <c r="D1713" s="19" t="s">
@@ -57576,13 +57742,13 @@
       <c r="B1714" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C1714" s="55">
+      <c r="C1714" s="54">
         <v>46304</v>
       </c>
-      <c r="D1714" s="52" t="s">
+      <c r="D1714" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1714" s="52" t="s">
+      <c r="E1714" s="51" t="s">
         <v>18</v>
       </c>
       <c r="F1714" s="4">
@@ -57605,19 +57771,19 @@
       </c>
     </row>
     <row r="1715" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1715" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1715" s="56" t="s">
+      <c r="A1715" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1715" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="C1715" s="54">
+      <c r="C1715" s="53">
         <v>46304</v>
       </c>
-      <c r="D1715" s="56" t="s">
+      <c r="D1715" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1715" s="56" t="s">
+      <c r="E1715" s="55" t="s">
         <v>19</v>
       </c>
       <c r="F1715" s="9">
@@ -57640,19 +57806,19 @@
       </c>
     </row>
     <row r="1716" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1716" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1716" s="52" t="s">
+      <c r="A1716" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1716" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1716" s="55">
+      <c r="C1716" s="54">
         <v>46304</v>
       </c>
-      <c r="D1716" s="52" t="s">
+      <c r="D1716" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1716" s="52" t="s">
+      <c r="E1716" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F1716" s="4">
@@ -57675,19 +57841,19 @@
       </c>
     </row>
     <row r="1717" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1717" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1717" s="56" t="s">
+      <c r="A1717" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1717" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1717" s="54">
+      <c r="C1717" s="53">
         <v>46304</v>
       </c>
-      <c r="D1717" s="56" t="s">
+      <c r="D1717" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1717" s="56" t="s">
+      <c r="E1717" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1717" s="9">
@@ -57710,19 +57876,19 @@
       </c>
     </row>
     <row r="1718" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1718" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1718" s="52" t="s">
+      <c r="A1718" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1718" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1718" s="55">
+      <c r="C1718" s="54">
         <v>46304</v>
       </c>
-      <c r="D1718" s="52" t="s">
+      <c r="D1718" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1718" s="52" t="s">
+      <c r="E1718" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F1718" s="4">
@@ -57751,7 +57917,7 @@
       <c r="B1719" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C1719" s="54">
+      <c r="C1719" s="53">
         <v>46304</v>
       </c>
       <c r="D1719" s="19" t="s">
@@ -57780,19 +57946,19 @@
       </c>
     </row>
     <row r="1720" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1720" s="52" t="s">
+      <c r="A1720" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="B1720" s="52" t="s">
+      <c r="B1720" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="C1720" s="55">
+      <c r="C1720" s="54">
         <v>46304</v>
       </c>
-      <c r="D1720" s="52" t="s">
+      <c r="D1720" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1720" s="52" t="s">
+      <c r="E1720" s="51" t="s">
         <v>311</v>
       </c>
       <c r="F1720" s="4">
@@ -57821,7 +57987,7 @@
       <c r="B1721" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C1721" s="54">
+      <c r="C1721" s="53">
         <v>46304</v>
       </c>
       <c r="D1721" s="19" t="s">
@@ -57856,7 +58022,7 @@
       <c r="B1722" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="C1722" s="55">
+      <c r="C1722" s="54">
         <v>46304</v>
       </c>
       <c r="D1722" s="19" t="s">
@@ -57885,19 +58051,19 @@
       </c>
     </row>
     <row r="1723" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1723" s="56" t="s">
+      <c r="A1723" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B1723" s="56" t="s">
+      <c r="B1723" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="C1723" s="54">
+      <c r="C1723" s="53">
         <v>46304</v>
       </c>
-      <c r="D1723" s="56" t="s">
+      <c r="D1723" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1723" s="56" t="s">
+      <c r="E1723" s="55" t="s">
         <v>23</v>
       </c>
       <c r="F1723" s="9" t="s">
@@ -57924,13 +58090,13 @@
       <c r="B1724" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="C1724" s="55">
+      <c r="C1724" s="54">
         <v>46304</v>
       </c>
-      <c r="D1724" s="52" t="s">
+      <c r="D1724" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1724" s="52" t="s">
+      <c r="E1724" s="51" t="s">
         <v>310</v>
       </c>
       <c r="F1724" s="4" t="s">
@@ -57957,13 +58123,13 @@
       <c r="B1725" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="C1725" s="54">
+      <c r="C1725" s="53">
         <v>46304</v>
       </c>
-      <c r="D1725" s="56" t="s">
+      <c r="D1725" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1725" s="56" t="s">
+      <c r="E1725" s="55" t="s">
         <v>219</v>
       </c>
       <c r="F1725" s="9" t="s">
@@ -57990,7 +58156,7 @@
       <c r="B1726" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C1726" s="55">
+      <c r="C1726" s="54">
         <v>46304</v>
       </c>
       <c r="D1726" s="19" t="s">
@@ -58025,7 +58191,7 @@
       <c r="B1727" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="C1727" s="54">
+      <c r="C1727" s="53">
         <v>46304</v>
       </c>
       <c r="D1727" s="19" t="s">
@@ -58058,7 +58224,7 @@
       <c r="B1728" s="19" t="s">
         <v>578</v>
       </c>
-      <c r="C1728" s="55">
+      <c r="C1728" s="54">
         <v>46304</v>
       </c>
       <c r="D1728" s="19" t="s">
@@ -58093,7 +58259,7 @@
       <c r="B1729" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1729" s="54">
+      <c r="C1729" s="53">
         <v>46304</v>
       </c>
       <c r="D1729" s="19" t="s">
@@ -58114,7 +58280,9 @@
       <c r="I1729" s="14" t="s">
         <v>733</v>
       </c>
-      <c r="J1729" s="13"/>
+      <c r="J1729" s="14" t="s">
+        <v>185</v>
+      </c>
       <c r="K1729" s="14" t="s">
         <v>286</v>
       </c>
@@ -58126,7 +58294,7 @@
       <c r="B1730" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1730" s="55">
+      <c r="C1730" s="54">
         <v>46304</v>
       </c>
       <c r="D1730" s="19" t="s">
@@ -58155,13 +58323,13 @@
       <c r="B1731" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C1731" s="54">
+      <c r="C1731" s="53">
         <v>46305</v>
       </c>
-      <c r="D1731" s="56" t="s">
+      <c r="D1731" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1731" s="56" t="s">
+      <c r="E1731" s="55" t="s">
         <v>18</v>
       </c>
       <c r="F1731" s="9">
@@ -58176,7 +58344,9 @@
       <c r="I1731" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="J1731" s="8"/>
+      <c r="J1731" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1731" s="9" t="s">
         <v>286</v>
       </c>
@@ -58188,7 +58358,7 @@
       <c r="B1732" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C1732" s="55">
+      <c r="C1732" s="54">
         <v>46305</v>
       </c>
       <c r="D1732" s="29" t="s">
@@ -58213,7 +58383,7 @@
       <c r="B1733" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C1733" s="54">
+      <c r="C1733" s="53">
         <v>46305</v>
       </c>
       <c r="D1733" s="29" t="s">
@@ -58222,8 +58392,8 @@
       <c r="E1733" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="F1733" s="58"/>
-      <c r="G1733" s="58"/>
+      <c r="F1733" s="57"/>
+      <c r="G1733" s="57"/>
       <c r="H1733" s="17" t="s">
         <v>26</v>
       </c>
@@ -58238,7 +58408,7 @@
       <c r="B1734" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C1734" s="55">
+      <c r="C1734" s="54">
         <v>46305</v>
       </c>
       <c r="D1734" s="19" t="s">
@@ -58261,19 +58431,19 @@
       </c>
     </row>
     <row r="1735" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1735" s="56" t="s">
+      <c r="A1735" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="B1735" s="56" t="s">
+      <c r="B1735" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="C1735" s="54">
+      <c r="C1735" s="53">
         <v>46305</v>
       </c>
-      <c r="D1735" s="56" t="s">
+      <c r="D1735" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1735" s="56" t="s">
+      <c r="E1735" s="55" t="s">
         <v>311</v>
       </c>
       <c r="F1735" s="9">
@@ -58302,7 +58472,7 @@
       <c r="B1736" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C1736" s="55">
+      <c r="C1736" s="54">
         <v>46305</v>
       </c>
       <c r="D1736" s="29" t="s">
@@ -58327,7 +58497,7 @@
       <c r="B1737" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="C1737" s="54">
+      <c r="C1737" s="53">
         <v>46305</v>
       </c>
       <c r="D1737" s="29" t="s">
@@ -58352,7 +58522,7 @@
       <c r="B1738" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C1738" s="55">
+      <c r="C1738" s="54">
         <v>46305</v>
       </c>
       <c r="D1738" s="29" t="s">
@@ -58377,7 +58547,7 @@
       <c r="B1739" s="29" t="s">
         <v>309</v>
       </c>
-      <c r="C1739" s="54">
+      <c r="C1739" s="53">
         <v>46305</v>
       </c>
       <c r="D1739" s="29" t="s">
@@ -58402,13 +58572,13 @@
       <c r="B1740" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C1740" s="55">
+      <c r="C1740" s="54">
         <v>46305</v>
       </c>
-      <c r="D1740" s="52" t="s">
+      <c r="D1740" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1740" s="52" t="s">
+      <c r="E1740" s="51" t="s">
         <v>219</v>
       </c>
       <c r="F1740" s="4" t="s">
@@ -58433,13 +58603,13 @@
       <c r="B1741" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C1741" s="54">
+      <c r="C1741" s="53">
         <v>46305</v>
       </c>
-      <c r="D1741" s="56" t="s">
+      <c r="D1741" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1741" s="56" t="s">
+      <c r="E1741" s="55" t="s">
         <v>29</v>
       </c>
       <c r="F1741" s="9">
@@ -58455,7 +58625,7 @@
         <v>738</v>
       </c>
       <c r="J1741" s="9" t="s">
-        <v>16</v>
+        <v>185</v>
       </c>
       <c r="K1741" s="9" t="s">
         <v>286</v>
@@ -58468,7 +58638,7 @@
       <c r="B1742" s="29" t="s">
         <v>501</v>
       </c>
-      <c r="C1742" s="55">
+      <c r="C1742" s="54">
         <v>46305</v>
       </c>
       <c r="D1742" s="29" t="s">
@@ -58493,13 +58663,13 @@
       <c r="B1743" s="31" t="s">
         <v>578</v>
       </c>
-      <c r="C1743" s="54">
+      <c r="C1743" s="53">
         <v>46305</v>
       </c>
-      <c r="D1743" s="56" t="s">
+      <c r="D1743" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1743" s="56" t="s">
+      <c r="E1743" s="55" t="s">
         <v>579</v>
       </c>
       <c r="F1743" s="9" t="s">
@@ -58524,7 +58694,7 @@
       <c r="B1744" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1744" s="55">
+      <c r="C1744" s="54">
         <v>46306</v>
       </c>
       <c r="D1744" s="19" t="s">
@@ -58559,13 +58729,13 @@
       <c r="B1745" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C1745" s="54">
+      <c r="C1745" s="53">
         <v>46306</v>
       </c>
-      <c r="D1745" s="56" t="s">
+      <c r="D1745" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1745" s="56" t="s">
+      <c r="E1745" s="55" t="s">
         <v>18</v>
       </c>
       <c r="F1745" s="20">
@@ -58594,7 +58764,7 @@
       <c r="B1746" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C1746" s="55">
+      <c r="C1746" s="54">
         <v>46306</v>
       </c>
       <c r="D1746" s="29" t="s">
@@ -58619,7 +58789,7 @@
       <c r="B1747" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C1747" s="54">
+      <c r="C1747" s="53">
         <v>46306</v>
       </c>
       <c r="D1747" s="29" t="s">
@@ -58644,7 +58814,7 @@
       <c r="B1748" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C1748" s="55">
+      <c r="C1748" s="54">
         <v>46306</v>
       </c>
       <c r="D1748" s="29" t="s">
@@ -58663,19 +58833,19 @@
       <c r="K1748" s="16"/>
     </row>
     <row r="1749" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1749" s="56" t="s">
+      <c r="A1749" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="B1749" s="56" t="s">
+      <c r="B1749" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="C1749" s="54">
+      <c r="C1749" s="53">
         <v>46306</v>
       </c>
-      <c r="D1749" s="56" t="s">
+      <c r="D1749" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1749" s="56" t="s">
+      <c r="E1749" s="55" t="s">
         <v>311</v>
       </c>
       <c r="F1749" s="9">
@@ -58704,7 +58874,7 @@
       <c r="B1750" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C1750" s="55">
+      <c r="C1750" s="54">
         <v>46306</v>
       </c>
       <c r="D1750" s="29" t="s">
@@ -58729,7 +58899,7 @@
       <c r="B1751" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="C1751" s="54">
+      <c r="C1751" s="53">
         <v>46306</v>
       </c>
       <c r="D1751" s="29" t="s">
@@ -58754,7 +58924,7 @@
       <c r="B1752" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C1752" s="55">
+      <c r="C1752" s="54">
         <v>46306</v>
       </c>
       <c r="D1752" s="29" t="s">
@@ -58779,7 +58949,7 @@
       <c r="B1753" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="C1753" s="54">
+      <c r="C1753" s="53">
         <v>46306</v>
       </c>
       <c r="D1753" s="19" t="s">
@@ -58808,7 +58978,7 @@
       <c r="B1754" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="C1754" s="55">
+      <c r="C1754" s="54">
         <v>46306</v>
       </c>
       <c r="D1754" s="29" t="s">
@@ -58833,16 +59003,16 @@
       <c r="B1755" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C1755" s="54">
+      <c r="C1755" s="53">
         <v>46306</v>
       </c>
-      <c r="D1755" s="56" t="s">
+      <c r="D1755" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1755" s="56" t="s">
+      <c r="E1755" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="F1755" s="60">
+      <c r="F1755" s="59">
         <v>400944893</v>
       </c>
       <c r="G1755" s="21">
@@ -58854,7 +59024,9 @@
       <c r="I1755" s="9" t="s">
         <v>743</v>
       </c>
-      <c r="J1755" s="8"/>
+      <c r="J1755" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K1755" s="9" t="s">
         <v>236</v>
       </c>
@@ -58866,7 +59038,7 @@
       <c r="B1756" s="29" t="s">
         <v>501</v>
       </c>
-      <c r="C1756" s="55">
+      <c r="C1756" s="54">
         <v>46306</v>
       </c>
       <c r="D1756" s="29" t="s">
@@ -58891,13 +59063,13 @@
       <c r="B1757" s="31" t="s">
         <v>578</v>
       </c>
-      <c r="C1757" s="54">
+      <c r="C1757" s="53">
         <v>46306</v>
       </c>
-      <c r="D1757" s="56" t="s">
+      <c r="D1757" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1757" s="56" t="s">
+      <c r="E1757" s="55" t="s">
         <v>579</v>
       </c>
       <c r="F1757" s="9">
@@ -58926,7 +59098,7 @@
       <c r="B1758" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1758" s="55">
+      <c r="C1758" s="54">
         <v>46307</v>
       </c>
       <c r="D1758" s="19" t="s">
@@ -58961,13 +59133,13 @@
       <c r="B1759" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C1759" s="54">
+      <c r="C1759" s="53">
         <v>46307</v>
       </c>
-      <c r="D1759" s="56" t="s">
+      <c r="D1759" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1759" s="56" t="s">
+      <c r="E1759" s="55" t="s">
         <v>18</v>
       </c>
       <c r="F1759" s="9">
@@ -58996,7 +59168,7 @@
       <c r="B1760" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C1760" s="55">
+      <c r="C1760" s="54">
         <v>46307</v>
       </c>
       <c r="D1760" s="29" t="s">
@@ -59021,7 +59193,7 @@
       <c r="B1761" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C1761" s="54">
+      <c r="C1761" s="53">
         <v>46307</v>
       </c>
       <c r="D1761" s="29" t="s">
@@ -59046,7 +59218,7 @@
       <c r="B1762" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C1762" s="55">
+      <c r="C1762" s="54">
         <v>46307</v>
       </c>
       <c r="D1762" s="29" t="s">
@@ -59065,19 +59237,19 @@
       <c r="K1762" s="16"/>
     </row>
     <row r="1763" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1763" s="56" t="s">
+      <c r="A1763" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="B1763" s="56" t="s">
+      <c r="B1763" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="C1763" s="54">
+      <c r="C1763" s="53">
         <v>46307</v>
       </c>
-      <c r="D1763" s="56" t="s">
+      <c r="D1763" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1763" s="56" t="s">
+      <c r="E1763" s="55" t="s">
         <v>311</v>
       </c>
       <c r="F1763" s="9">
@@ -59106,7 +59278,7 @@
       <c r="B1764" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C1764" s="55">
+      <c r="C1764" s="54">
         <v>46307</v>
       </c>
       <c r="D1764" s="29" t="s">
@@ -59131,7 +59303,7 @@
       <c r="B1765" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="C1765" s="54">
+      <c r="C1765" s="53">
         <v>46307</v>
       </c>
       <c r="D1765" s="29" t="s">
@@ -59156,7 +59328,7 @@
       <c r="B1766" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C1766" s="55">
+      <c r="C1766" s="54">
         <v>46307</v>
       </c>
       <c r="D1766" s="29" t="s">
@@ -59181,7 +59353,7 @@
       <c r="B1767" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="C1767" s="54">
+      <c r="C1767" s="53">
         <v>46307</v>
       </c>
       <c r="D1767" s="19" t="s">
@@ -59210,7 +59382,7 @@
       <c r="B1768" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="C1768" s="55">
+      <c r="C1768" s="54">
         <v>46307</v>
       </c>
       <c r="D1768" s="29" t="s">
@@ -59235,13 +59407,13 @@
       <c r="B1769" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C1769" s="54">
+      <c r="C1769" s="53">
         <v>46307</v>
       </c>
-      <c r="D1769" s="56" t="s">
+      <c r="D1769" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1769" s="56" t="s">
+      <c r="E1769" s="55" t="s">
         <v>29</v>
       </c>
       <c r="F1769" s="9">
@@ -59270,13 +59442,13 @@
       <c r="B1770" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C1770" s="55">
+      <c r="C1770" s="54">
         <v>46307</v>
       </c>
-      <c r="D1770" s="52" t="s">
+      <c r="D1770" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1770" s="52" t="s">
+      <c r="E1770" s="51" t="s">
         <v>29</v>
       </c>
       <c r="F1770" s="4">
@@ -59305,7 +59477,7 @@
       <c r="B1771" s="29" t="s">
         <v>501</v>
       </c>
-      <c r="C1771" s="54">
+      <c r="C1771" s="53">
         <v>46307</v>
       </c>
       <c r="D1771" s="29" t="s">
@@ -59330,13 +59502,13 @@
       <c r="B1772" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="C1772" s="55">
+      <c r="C1772" s="54">
         <v>46307</v>
       </c>
-      <c r="D1772" s="52" t="s">
+      <c r="D1772" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1772" s="52" t="s">
+      <c r="E1772" s="51" t="s">
         <v>579</v>
       </c>
       <c r="F1772" s="4">
@@ -59359,19 +59531,19 @@
       </c>
     </row>
     <row r="1773" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1773" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1773" s="56" t="s">
+      <c r="A1773" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1773" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="C1773" s="54">
+      <c r="C1773" s="53">
         <v>46308</v>
       </c>
-      <c r="D1773" s="56" t="s">
+      <c r="D1773" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1773" s="56" t="s">
+      <c r="E1773" s="55" t="s">
         <v>510</v>
       </c>
       <c r="F1773" s="9">
@@ -59400,13 +59572,13 @@
       <c r="B1774" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C1774" s="55">
+      <c r="C1774" s="54">
         <v>46308</v>
       </c>
-      <c r="D1774" s="52" t="s">
+      <c r="D1774" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1774" s="52" t="s">
+      <c r="E1774" s="51" t="s">
         <v>18</v>
       </c>
       <c r="F1774" s="4">
@@ -59435,7 +59607,7 @@
       <c r="B1775" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C1775" s="54">
+      <c r="C1775" s="53">
         <v>46308</v>
       </c>
       <c r="D1775" s="29" t="s">
@@ -59454,19 +59626,19 @@
       <c r="K1775" s="16"/>
     </row>
     <row r="1776" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1776" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1776" s="52" t="s">
+      <c r="A1776" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1776" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1776" s="55">
+      <c r="C1776" s="54">
         <v>46308</v>
       </c>
-      <c r="D1776" s="52" t="s">
+      <c r="D1776" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1776" s="52" t="s">
+      <c r="E1776" s="51" t="s">
         <v>31</v>
       </c>
       <c r="F1776" s="7">
@@ -59489,19 +59661,19 @@
       </c>
     </row>
     <row r="1777" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1777" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1777" s="56" t="s">
+      <c r="A1777" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1777" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1777" s="54">
+      <c r="C1777" s="53">
         <v>46308</v>
       </c>
-      <c r="D1777" s="56" t="s">
+      <c r="D1777" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1777" s="56" t="s">
+      <c r="E1777" s="55" t="s">
         <v>31</v>
       </c>
       <c r="F1777" s="7">
@@ -59524,19 +59696,19 @@
       </c>
     </row>
     <row r="1778" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1778" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1778" s="52" t="s">
+      <c r="A1778" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1778" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="C1778" s="55">
+      <c r="C1778" s="54">
         <v>46308</v>
       </c>
-      <c r="D1778" s="52" t="s">
+      <c r="D1778" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1778" s="52" t="s">
+      <c r="E1778" s="51" t="s">
         <v>134</v>
       </c>
       <c r="F1778" s="4">
@@ -59559,19 +59731,19 @@
       </c>
     </row>
     <row r="1779" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1779" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1779" s="56" t="s">
+      <c r="A1779" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1779" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="C1779" s="54">
+      <c r="C1779" s="53">
         <v>46308</v>
       </c>
-      <c r="D1779" s="56" t="s">
+      <c r="D1779" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1779" s="56" t="s">
+      <c r="E1779" s="55" t="s">
         <v>311</v>
       </c>
       <c r="F1779" s="9">
@@ -59600,7 +59772,7 @@
       <c r="B1780" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C1780" s="55">
+      <c r="C1780" s="54">
         <v>46308</v>
       </c>
       <c r="D1780" s="19" t="s">
@@ -59629,19 +59801,19 @@
       </c>
     </row>
     <row r="1781" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1781" s="56" t="s">
+      <c r="A1781" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="B1781" s="56" t="s">
+      <c r="B1781" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="C1781" s="54">
+      <c r="C1781" s="53">
         <v>46308</v>
       </c>
-      <c r="D1781" s="56" t="s">
+      <c r="D1781" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1781" s="56" t="s">
+      <c r="E1781" s="55" t="s">
         <v>335</v>
       </c>
       <c r="F1781" s="9">
@@ -59664,19 +59836,19 @@
       </c>
     </row>
     <row r="1782" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1782" s="52" t="s">
+      <c r="A1782" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B1782" s="52" t="s">
+      <c r="B1782" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="C1782" s="55">
+      <c r="C1782" s="54">
         <v>46308</v>
       </c>
-      <c r="D1782" s="52" t="s">
+      <c r="D1782" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1782" s="52" t="s">
+      <c r="E1782" s="51" t="s">
         <v>23</v>
       </c>
       <c r="F1782" s="4" t="s">
@@ -59705,13 +59877,13 @@
       <c r="B1783" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="C1783" s="54">
+      <c r="C1783" s="53">
         <v>46308</v>
       </c>
-      <c r="D1783" s="56" t="s">
+      <c r="D1783" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1783" s="56" t="s">
+      <c r="E1783" s="55" t="s">
         <v>759</v>
       </c>
       <c r="F1783" s="9" t="s">
@@ -59740,16 +59912,16 @@
       <c r="B1784" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C1784" s="55">
+      <c r="C1784" s="54">
         <v>46308</v>
       </c>
-      <c r="D1784" s="52" t="s">
+      <c r="D1784" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1784" s="52" t="s">
+      <c r="E1784" s="51" t="s">
         <v>219</v>
       </c>
-      <c r="F1784" s="4" t="s">
+      <c r="F1784" s="7" t="s">
         <v>492</v>
       </c>
       <c r="G1784" s="12" t="s">
@@ -59775,16 +59947,16 @@
       <c r="B1785" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C1785" s="54">
+      <c r="C1785" s="53">
         <v>46308</v>
       </c>
-      <c r="D1785" s="56" t="s">
+      <c r="D1785" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1785" s="56" t="s">
+      <c r="E1785" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="F1785" s="9" t="s">
+      <c r="F1785" s="7" t="s">
         <v>492</v>
       </c>
       <c r="G1785" s="21" t="s">
@@ -59804,22 +59976,22 @@
       </c>
     </row>
     <row r="1786" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1786" s="52" t="s">
+      <c r="A1786" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B1786" s="52" t="s">
+      <c r="B1786" s="51" t="s">
         <v>501</v>
       </c>
-      <c r="C1786" s="55">
+      <c r="C1786" s="54">
         <v>46308</v>
       </c>
-      <c r="D1786" s="52" t="s">
+      <c r="D1786" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1786" s="52" t="s">
+      <c r="E1786" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="F1786" s="4" t="s">
+      <c r="F1786" s="7" t="s">
         <v>601</v>
       </c>
       <c r="G1786" s="4" t="s">
@@ -59845,16 +60017,16 @@
       <c r="B1787" s="31" t="s">
         <v>578</v>
       </c>
-      <c r="C1787" s="54">
+      <c r="C1787" s="53">
         <v>46308</v>
       </c>
-      <c r="D1787" s="56" t="s">
+      <c r="D1787" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1787" s="56" t="s">
+      <c r="E1787" s="55" t="s">
         <v>579</v>
       </c>
-      <c r="F1787" s="9" t="s">
+      <c r="F1787" s="7" t="s">
         <v>749</v>
       </c>
       <c r="G1787" s="21" t="s">
@@ -59880,7 +60052,7 @@
       <c r="B1788" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1788" s="55">
+      <c r="C1788" s="54">
         <v>46309</v>
       </c>
       <c r="D1788" s="19" t="s">
@@ -59889,7 +60061,7 @@
       <c r="E1788" s="19" t="s">
         <v>510</v>
       </c>
-      <c r="F1788" s="13"/>
+      <c r="F1788" s="34"/>
       <c r="G1788" s="13"/>
       <c r="H1788" s="14" t="s">
         <v>21</v>
@@ -59909,13 +60081,13 @@
       <c r="B1789" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C1789" s="54">
+      <c r="C1789" s="53">
         <v>46309</v>
       </c>
-      <c r="D1789" s="56" t="s">
+      <c r="D1789" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1789" s="56" t="s">
+      <c r="E1789" s="55" t="s">
         <v>18</v>
       </c>
       <c r="F1789" s="7">
@@ -59925,7 +60097,7 @@
         <v>146614161</v>
       </c>
       <c r="H1789" s="9" t="s">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="I1789" s="9" t="s">
         <v>322</v>
@@ -59938,29 +60110,29 @@
       </c>
     </row>
     <row r="1790" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1790" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1790" s="52" t="s">
+      <c r="A1790" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1790" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="C1790" s="55">
+      <c r="C1790" s="54">
         <v>46309</v>
       </c>
-      <c r="D1790" s="52" t="s">
+      <c r="D1790" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1790" s="52" t="s">
+      <c r="E1790" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F1790" s="4">
+      <c r="F1790" s="7">
         <v>400943840</v>
       </c>
       <c r="G1790" s="12">
         <v>146606293</v>
       </c>
       <c r="H1790" s="4" t="s">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="I1790" s="4" t="s">
         <v>768</v>
@@ -59979,7 +60151,7 @@
       <c r="B1791" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C1791" s="54">
+      <c r="C1791" s="53">
         <v>46309</v>
       </c>
       <c r="D1791" s="19" t="s">
@@ -60002,19 +60174,19 @@
       </c>
     </row>
     <row r="1792" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1792" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1792" s="52" t="s">
+      <c r="A1792" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1792" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="C1792" s="55">
+      <c r="C1792" s="54">
         <v>46309</v>
       </c>
-      <c r="D1792" s="52" t="s">
+      <c r="D1792" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1792" s="52" t="s">
+      <c r="E1792" s="51" t="s">
         <v>134</v>
       </c>
       <c r="F1792" s="7">
@@ -60024,7 +60196,7 @@
         <v>146614961</v>
       </c>
       <c r="H1792" s="4" t="s">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="I1792" s="4" t="s">
         <v>243</v>
@@ -60036,46 +60208,58 @@
         <v>769</v>
       </c>
     </row>
-    <row r="1793" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1793" s="56" t="s">
+    <row r="1793" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1793" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="B1793" s="56" t="s">
+      <c r="B1793" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="C1793" s="54">
+      <c r="C1793" s="53">
         <v>46309</v>
       </c>
-      <c r="D1793" s="56" t="s">
+      <c r="D1793" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1793" s="56" t="s">
+      <c r="E1793" s="55" t="s">
         <v>311</v>
       </c>
-      <c r="F1793" s="8"/>
-      <c r="G1793" s="8"/>
-      <c r="H1793" s="8"/>
-      <c r="I1793" s="8"/>
-      <c r="J1793" s="8"/>
-      <c r="K1793" s="8"/>
+      <c r="F1793" s="7">
+        <v>400910821</v>
+      </c>
+      <c r="G1793" s="21">
+        <v>400910821</v>
+      </c>
+      <c r="H1793" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1793" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="J1793" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1793" s="9" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="1794" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1794" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1794" s="52" t="s">
+      <c r="A1794" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1794" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="C1794" s="55">
+      <c r="C1794" s="54">
         <v>46309</v>
       </c>
-      <c r="D1794" s="52" t="s">
+      <c r="D1794" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1794" s="52" t="s">
+      <c r="E1794" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="F1794" s="4">
+      <c r="F1794" s="7">
         <v>400945391</v>
       </c>
       <c r="G1794" s="12">
@@ -60093,22 +60277,22 @@
       </c>
     </row>
     <row r="1795" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1795" s="56" t="s">
+      <c r="A1795" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="B1795" s="56" t="s">
+      <c r="B1795" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="C1795" s="54">
+      <c r="C1795" s="53">
         <v>46309</v>
       </c>
-      <c r="D1795" s="56" t="s">
+      <c r="D1795" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1795" s="56" t="s">
+      <c r="E1795" s="55" t="s">
         <v>335</v>
       </c>
-      <c r="F1795" s="8"/>
+      <c r="F1795" s="44"/>
       <c r="G1795" s="8"/>
       <c r="H1795" s="8"/>
       <c r="I1795" s="8"/>
@@ -60116,22 +60300,22 @@
       <c r="K1795" s="8"/>
     </row>
     <row r="1796" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A1796" s="52" t="s">
+      <c r="A1796" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B1796" s="52" t="s">
+      <c r="B1796" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="C1796" s="55">
+      <c r="C1796" s="54">
         <v>46309</v>
       </c>
-      <c r="D1796" s="52" t="s">
+      <c r="D1796" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1796" s="52" t="s">
+      <c r="E1796" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="F1796" s="4" t="s">
+      <c r="F1796" s="7" t="s">
         <v>749</v>
       </c>
       <c r="G1796" s="12" t="s">
@@ -60157,16 +60341,16 @@
       <c r="B1797" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="C1797" s="54">
+      <c r="C1797" s="53">
         <v>46309</v>
       </c>
-      <c r="D1797" s="56" t="s">
+      <c r="D1797" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1797" s="56" t="s">
+      <c r="E1797" s="55" t="s">
         <v>759</v>
       </c>
-      <c r="F1797" s="9" t="s">
+      <c r="F1797" s="7" t="s">
         <v>749</v>
       </c>
       <c r="G1797" s="21" t="s">
@@ -60192,16 +60376,16 @@
       <c r="B1798" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C1798" s="55">
+      <c r="C1798" s="54">
         <v>46309</v>
       </c>
-      <c r="D1798" s="52" t="s">
+      <c r="D1798" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1798" s="52" t="s">
+      <c r="E1798" s="51" t="s">
         <v>219</v>
       </c>
-      <c r="F1798" s="4" t="s">
+      <c r="F1798" s="7" t="s">
         <v>492</v>
       </c>
       <c r="G1798" s="12" t="s">
@@ -60227,16 +60411,16 @@
       <c r="B1799" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C1799" s="54">
+      <c r="C1799" s="53">
         <v>46309</v>
       </c>
-      <c r="D1799" s="56" t="s">
+      <c r="D1799" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1799" s="56" t="s">
+      <c r="E1799" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="F1799" s="9" t="s">
+      <c r="F1799" s="7" t="s">
         <v>749</v>
       </c>
       <c r="G1799" s="21" t="s">
@@ -60256,22 +60440,22 @@
       </c>
     </row>
     <row r="1800" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A1800" s="52" t="s">
+      <c r="A1800" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B1800" s="52" t="s">
+      <c r="B1800" s="51" t="s">
         <v>501</v>
       </c>
-      <c r="C1800" s="55">
+      <c r="C1800" s="54">
         <v>46309</v>
       </c>
-      <c r="D1800" s="52" t="s">
+      <c r="D1800" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1800" s="52" t="s">
+      <c r="E1800" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="F1800" s="4" t="s">
+      <c r="F1800" s="7" t="s">
         <v>749</v>
       </c>
       <c r="G1800" s="12" t="s">
@@ -60297,16 +60481,16 @@
       <c r="B1801" s="31" t="s">
         <v>578</v>
       </c>
-      <c r="C1801" s="54">
+      <c r="C1801" s="53">
         <v>46309</v>
       </c>
-      <c r="D1801" s="56" t="s">
+      <c r="D1801" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1801" s="56" t="s">
+      <c r="E1801" s="55" t="s">
         <v>579</v>
       </c>
-      <c r="F1801" s="9" t="s">
+      <c r="F1801" s="7" t="s">
         <v>749</v>
       </c>
       <c r="G1801" s="21" t="s">
@@ -60332,7 +60516,7 @@
       <c r="B1802" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C1802" s="55">
+      <c r="C1802" s="54">
         <v>46310</v>
       </c>
       <c r="D1802" s="19" t="s">
@@ -60341,7 +60525,7 @@
       <c r="E1802" s="19" t="s">
         <v>510</v>
       </c>
-      <c r="F1802" s="13"/>
+      <c r="F1802" s="34"/>
       <c r="G1802" s="13"/>
       <c r="H1802" s="14" t="s">
         <v>21</v>
@@ -60359,23 +60543,23 @@
       <c r="B1803" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C1803" s="54">
+      <c r="C1803" s="53">
         <v>46310</v>
       </c>
-      <c r="D1803" s="56" t="s">
+      <c r="D1803" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1803" s="56" t="s">
+      <c r="E1803" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="F1803" s="20">
+      <c r="F1803" s="7">
         <v>400944037</v>
       </c>
-      <c r="G1803" s="20">
+      <c r="G1803" s="21">
         <v>146607379</v>
       </c>
       <c r="H1803" s="9" t="s">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="I1803" s="9" t="s">
         <v>777</v>
@@ -60386,29 +60570,29 @@
       </c>
     </row>
     <row r="1804" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1804" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1804" s="52" t="s">
+      <c r="A1804" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1804" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="C1804" s="55">
+      <c r="C1804" s="54">
         <v>46310</v>
       </c>
-      <c r="D1804" s="52" t="s">
+      <c r="D1804" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1804" s="52" t="s">
+      <c r="E1804" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F1804" s="20">
+      <c r="F1804" s="7">
         <v>400944892</v>
       </c>
-      <c r="G1804" s="23">
+      <c r="G1804" s="12">
         <v>146612784</v>
       </c>
       <c r="H1804" s="4" t="s">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="I1804" s="4" t="s">
         <v>778</v>
@@ -60419,29 +60603,29 @@
       </c>
     </row>
     <row r="1805" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1805" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1805" s="56" t="s">
+      <c r="A1805" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1805" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1805" s="54">
+      <c r="C1805" s="53">
         <v>46310</v>
       </c>
-      <c r="D1805" s="56" t="s">
+      <c r="D1805" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1805" s="56" t="s">
+      <c r="E1805" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="F1805" s="9">
-        <v>146616503</v>
+      <c r="F1805" s="7">
+        <v>400945531</v>
       </c>
       <c r="G1805" s="21">
         <v>146616503</v>
       </c>
       <c r="H1805" s="9" t="s">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="I1805" s="9" t="s">
         <v>779</v>
@@ -60452,25 +60636,25 @@
       </c>
     </row>
     <row r="1806" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1806" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1806" s="52" t="s">
+      <c r="A1806" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1806" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1806" s="55">
+      <c r="C1806" s="54">
         <v>46310</v>
       </c>
-      <c r="D1806" s="52" t="s">
+      <c r="D1806" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1806" s="52" t="s">
+      <c r="E1806" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="F1806" s="4">
-        <v>146616718</v>
-      </c>
-      <c r="G1806" s="4">
+      <c r="F1806" s="7">
+        <v>400945529</v>
+      </c>
+      <c r="G1806" s="12">
         <v>146616718</v>
       </c>
       <c r="H1806" s="4" t="s">
@@ -60485,29 +60669,29 @@
       </c>
     </row>
     <row r="1807" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1807" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1807" s="56" t="s">
+      <c r="A1807" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1807" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C1807" s="54">
+      <c r="C1807" s="53">
         <v>46310</v>
       </c>
-      <c r="D1807" s="56" t="s">
+      <c r="D1807" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1807" s="56" t="s">
+      <c r="E1807" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="F1807" s="9">
+      <c r="F1807" s="7">
+        <v>400945532</v>
+      </c>
+      <c r="G1807" s="21">
         <v>146616789</v>
       </c>
-      <c r="G1807" s="9">
-        <v>146616789</v>
-      </c>
       <c r="H1807" s="9" t="s">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="I1807" s="9" t="s">
         <v>780</v>
@@ -60518,29 +60702,29 @@
       </c>
     </row>
     <row r="1808" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1808" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1808" s="52" t="s">
+      <c r="A1808" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1808" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="C1808" s="55">
+      <c r="C1808" s="54">
         <v>46310</v>
       </c>
-      <c r="D1808" s="52" t="s">
+      <c r="D1808" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1808" s="52" t="s">
+      <c r="E1808" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="F1808" s="4">
+      <c r="F1808" s="7">
+        <v>400945530</v>
+      </c>
+      <c r="G1808" s="12">
         <v>146616750</v>
       </c>
-      <c r="G1808" s="4">
-        <v>146616750</v>
-      </c>
       <c r="H1808" s="4" t="s">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="I1808" s="4" t="s">
         <v>781</v>
@@ -60551,19 +60735,19 @@
       </c>
     </row>
     <row r="1809" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1809" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1809" s="56" t="s">
+      <c r="A1809" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1809" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="C1809" s="54">
+      <c r="C1809" s="53">
         <v>46310</v>
       </c>
-      <c r="D1809" s="56" t="s">
+      <c r="D1809" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1809" s="56" t="s">
+      <c r="E1809" s="55" t="s">
         <v>134</v>
       </c>
       <c r="F1809" s="7">
@@ -60573,7 +60757,7 @@
         <v>146607477</v>
       </c>
       <c r="H1809" s="9" t="s">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="I1809" s="9" t="s">
         <v>782</v>
@@ -60583,53 +60767,63 @@
         <v>286</v>
       </c>
     </row>
-    <row r="1810" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1810" s="52" t="s">
+    <row r="1810" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1810" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="B1810" s="52" t="s">
+      <c r="B1810" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="C1810" s="55">
+      <c r="C1810" s="54">
         <v>46310</v>
       </c>
-      <c r="D1810" s="52" t="s">
+      <c r="D1810" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1810" s="52" t="s">
+      <c r="E1810" s="51" t="s">
         <v>311</v>
       </c>
-      <c r="F1810" s="3"/>
-      <c r="G1810" s="3"/>
-      <c r="H1810" s="3"/>
-      <c r="I1810" s="3"/>
+      <c r="F1810" s="7">
+        <v>400938016</v>
+      </c>
+      <c r="G1810" s="12">
+        <v>400938016</v>
+      </c>
+      <c r="H1810" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1810" s="4" t="s">
+        <v>785</v>
+      </c>
       <c r="J1810" s="3"/>
-      <c r="K1810" s="3"/>
+      <c r="K1810" s="4" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="1811" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1811" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1811" s="56" t="s">
+      <c r="A1811" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1811" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="C1811" s="54">
+      <c r="C1811" s="53">
         <v>46310</v>
       </c>
-      <c r="D1811" s="56" t="s">
+      <c r="D1811" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1811" s="56" t="s">
+      <c r="E1811" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="F1811" s="9">
+      <c r="F1811" s="7">
         <v>400945390</v>
       </c>
       <c r="G1811" s="21">
         <v>145565949</v>
       </c>
       <c r="H1811" s="9" t="s">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="I1811" s="9" t="s">
         <v>783</v>
@@ -60640,50 +60834,62 @@
       </c>
     </row>
     <row r="1812" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1812" s="52" t="s">
+      <c r="A1812" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="B1812" s="52" t="s">
+      <c r="B1812" s="51" t="s">
         <v>334</v>
       </c>
-      <c r="C1812" s="55">
+      <c r="C1812" s="54">
         <v>46310</v>
       </c>
-      <c r="D1812" s="52" t="s">
+      <c r="D1812" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1812" s="52" t="s">
+      <c r="E1812" s="51" t="s">
         <v>335</v>
       </c>
-      <c r="F1812" s="3"/>
+      <c r="F1812" s="44"/>
       <c r="G1812" s="3"/>
       <c r="H1812" s="3"/>
       <c r="I1812" s="3"/>
       <c r="J1812" s="3"/>
       <c r="K1812" s="3"/>
     </row>
-    <row r="1813" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1813" s="56" t="s">
+    <row r="1813" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1813" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B1813" s="56" t="s">
+      <c r="B1813" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="C1813" s="54">
+      <c r="C1813" s="53">
         <v>46310</v>
       </c>
-      <c r="D1813" s="56" t="s">
+      <c r="D1813" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1813" s="56" t="s">
+      <c r="E1813" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="F1813" s="8"/>
-      <c r="G1813" s="8"/>
-      <c r="H1813" s="8"/>
-      <c r="I1813" s="8"/>
-      <c r="J1813" s="8"/>
-      <c r="K1813" s="8"/>
+      <c r="F1813" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1813" s="21" t="s">
+        <v>786</v>
+      </c>
+      <c r="H1813" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1813" s="9" t="s">
+        <v>787</v>
+      </c>
+      <c r="J1813" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1813" s="9" t="s">
+        <v>719</v>
+      </c>
     </row>
     <row r="1814" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1814" s="7" t="s">
@@ -60692,21 +60898,33 @@
       <c r="B1814" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="C1814" s="55">
+      <c r="C1814" s="54">
         <v>46310</v>
       </c>
-      <c r="D1814" s="52" t="s">
+      <c r="D1814" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1814" s="52" t="s">
+      <c r="E1814" s="51" t="s">
         <v>759</v>
       </c>
-      <c r="F1814" s="3"/>
-      <c r="G1814" s="3"/>
-      <c r="H1814" s="3"/>
-      <c r="I1814" s="3"/>
-      <c r="J1814" s="3"/>
-      <c r="K1814" s="3"/>
+      <c r="F1814" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1814" s="12" t="s">
+        <v>788</v>
+      </c>
+      <c r="H1814" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1814" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="J1814" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1814" s="4" t="s">
+        <v>719</v>
+      </c>
     </row>
     <row r="1815" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1815" s="31" t="s">
@@ -60715,95 +60933,1781 @@
       <c r="B1815" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="C1815" s="54">
+      <c r="C1815" s="53">
         <v>46310</v>
       </c>
-      <c r="D1815" s="56" t="s">
+      <c r="D1815" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1815" s="56" t="s">
+      <c r="E1815" s="55" t="s">
         <v>219</v>
       </c>
-      <c r="F1815" s="8"/>
-      <c r="G1815" s="8"/>
-      <c r="H1815" s="8"/>
-      <c r="I1815" s="8"/>
-      <c r="J1815" s="8"/>
-      <c r="K1815" s="8"/>
-    </row>
-    <row r="1816" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F1815" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="G1815" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="H1815" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1815" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="J1815" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1815" s="9" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1816" s="7" t="s">
         <v>56</v>
       </c>
       <c r="B1816" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C1816" s="55">
+      <c r="C1816" s="54">
         <v>46310</v>
       </c>
-      <c r="D1816" s="52" t="s">
+      <c r="D1816" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1816" s="52" t="s">
+      <c r="E1816" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="F1816" s="3"/>
-      <c r="G1816" s="3"/>
-      <c r="H1816" s="3"/>
-      <c r="I1816" s="3"/>
-      <c r="J1816" s="3"/>
-      <c r="K1816" s="3"/>
-    </row>
-    <row r="1817" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1817" s="56" t="s">
+      <c r="F1816" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="G1816" s="12" t="s">
+        <v>791</v>
+      </c>
+      <c r="H1816" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1816" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="J1816" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1816" s="4" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1817" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B1817" s="56" t="s">
+      <c r="B1817" s="55" t="s">
         <v>501</v>
       </c>
-      <c r="C1817" s="54">
+      <c r="C1817" s="53">
         <v>46310</v>
       </c>
-      <c r="D1817" s="56" t="s">
+      <c r="D1817" s="55" t="s">
         <v>645</v>
       </c>
-      <c r="E1817" s="56" t="s">
+      <c r="E1817" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="F1817" s="8"/>
-      <c r="G1817" s="8"/>
-      <c r="H1817" s="8"/>
-      <c r="I1817" s="8"/>
-      <c r="J1817" s="8"/>
-      <c r="K1817" s="8"/>
-    </row>
-    <row r="1818" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F1817" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1817" s="21" t="s">
+        <v>792</v>
+      </c>
+      <c r="H1817" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1817" s="9" t="s">
+        <v>787</v>
+      </c>
+      <c r="J1817" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1817" s="9" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1818" s="7" t="s">
         <v>56</v>
       </c>
       <c r="B1818" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="C1818" s="55">
+      <c r="C1818" s="54">
         <v>46310</v>
       </c>
-      <c r="D1818" s="52" t="s">
+      <c r="D1818" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="E1818" s="52" t="s">
+      <c r="E1818" s="51" t="s">
         <v>579</v>
       </c>
-      <c r="F1818" s="3"/>
-      <c r="G1818" s="3"/>
-      <c r="H1818" s="3"/>
-      <c r="I1818" s="3"/>
-      <c r="J1818" s="3"/>
-      <c r="K1818" s="3"/>
+      <c r="F1818" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="G1818" s="12" t="s">
+        <v>793</v>
+      </c>
+      <c r="H1818" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1818" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="J1818" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1818" s="4" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1819" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1819" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1819" s="53">
+        <v>46311</v>
+      </c>
+      <c r="D1819" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1819" s="19" t="s">
+        <v>510</v>
+      </c>
+      <c r="F1819" s="13"/>
+      <c r="G1819" s="13"/>
+      <c r="H1819" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1819" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="J1819" s="13"/>
+      <c r="K1819" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1820" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1820" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1820" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D1820" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1820" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1820" s="4">
+        <v>400945572</v>
+      </c>
+      <c r="G1820" s="12">
+        <v>146605045</v>
+      </c>
+      <c r="H1820" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1820" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="J1820" s="3"/>
+      <c r="K1820" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1821" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1821" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1821" s="53">
+        <v>46311</v>
+      </c>
+      <c r="D1821" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1821" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1821" s="9">
+        <v>400945571</v>
+      </c>
+      <c r="G1821" s="21">
+        <v>146608782</v>
+      </c>
+      <c r="H1821" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1821" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="J1821" s="8"/>
+      <c r="K1821" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1822" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1822" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1822" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D1822" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1822" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1822" s="4">
+        <v>400945569</v>
+      </c>
+      <c r="G1822" s="12">
+        <v>146607864</v>
+      </c>
+      <c r="H1822" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1822" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="J1822" s="3"/>
+      <c r="K1822" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1823" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1823" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1823" s="53">
+        <v>46311</v>
+      </c>
+      <c r="D1823" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1823" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1823" s="9">
+        <v>400945570</v>
+      </c>
+      <c r="G1823" s="21">
+        <v>146611075</v>
+      </c>
+      <c r="H1823" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1823" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="J1823" s="8"/>
+      <c r="K1823" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1824" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1824" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1824" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D1824" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1824" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1824" s="4">
+        <v>400945575</v>
+      </c>
+      <c r="G1824" s="12">
+        <v>146616636</v>
+      </c>
+      <c r="H1824" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1824" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="J1824" s="3"/>
+      <c r="K1824" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1825" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1825" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1825" s="53">
+        <v>46311</v>
+      </c>
+      <c r="D1825" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1825" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1825" s="9">
+        <v>400945562</v>
+      </c>
+      <c r="G1825" s="21">
+        <v>400945562</v>
+      </c>
+      <c r="H1825" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1825" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="J1825" s="8"/>
+      <c r="K1825" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1826" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1826" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1826" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D1826" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1826" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1826" s="4">
+        <v>400945576</v>
+      </c>
+      <c r="G1826" s="12">
+        <v>146617538</v>
+      </c>
+      <c r="H1826" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1826" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="J1826" s="3"/>
+      <c r="K1826" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1827" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1827" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1827" s="53">
+        <v>46311</v>
+      </c>
+      <c r="D1827" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1827" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1827" s="9">
+        <v>400939368</v>
+      </c>
+      <c r="G1827" s="21">
+        <v>400939368</v>
+      </c>
+      <c r="H1827" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1827" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="J1827" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1827" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1828" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1828" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1828" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D1828" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1828" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1828" s="4">
+        <v>146617640</v>
+      </c>
+      <c r="G1828" s="12">
+        <v>146617640</v>
+      </c>
+      <c r="H1828" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1828" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="J1828" s="3"/>
+      <c r="K1828" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1829" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1829" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1829" s="53">
+        <v>46311</v>
+      </c>
+      <c r="D1829" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1829" s="55" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1829" s="9">
+        <v>400945567</v>
+      </c>
+      <c r="G1829" s="21">
+        <v>146608671</v>
+      </c>
+      <c r="H1829" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1829" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="J1829" s="8"/>
+      <c r="K1829" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1830" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1830" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1830" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D1830" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1830" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1830" s="4">
+        <v>400945568</v>
+      </c>
+      <c r="G1830" s="12">
+        <v>146611079</v>
+      </c>
+      <c r="H1830" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1830" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="J1830" s="3"/>
+      <c r="K1830" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1831" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1831" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1831" s="53">
+        <v>46311</v>
+      </c>
+      <c r="D1831" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1831" s="55" t="s">
+        <v>372</v>
+      </c>
+      <c r="F1831" s="9">
+        <v>400945574</v>
+      </c>
+      <c r="G1831" s="21">
+        <v>146616142</v>
+      </c>
+      <c r="H1831" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1831" s="9" t="s">
+        <v>798</v>
+      </c>
+      <c r="J1831" s="8"/>
+      <c r="K1831" s="8"/>
+    </row>
+    <row r="1832" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1832" s="51" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1832" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1832" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D1832" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1832" s="51" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1832" s="3"/>
+      <c r="G1832" s="3"/>
+      <c r="H1832" s="3"/>
+      <c r="I1832" s="44"/>
+      <c r="J1832" s="44"/>
+      <c r="K1832" s="44"/>
+    </row>
+    <row r="1833" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1833" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1833" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1833" s="53">
+        <v>46311</v>
+      </c>
+      <c r="D1833" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1833" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1833" s="8"/>
+      <c r="G1833" s="8"/>
+      <c r="H1833" s="8"/>
+      <c r="I1833" s="8"/>
+      <c r="J1833" s="8"/>
+      <c r="K1833" s="8"/>
+    </row>
+    <row r="1834" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1834" s="51" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1834" s="51" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1834" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D1834" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1834" s="51" t="s">
+        <v>335</v>
+      </c>
+      <c r="F1834" s="3"/>
+      <c r="G1834" s="3"/>
+      <c r="H1834" s="3"/>
+      <c r="I1834" s="3"/>
+      <c r="J1834" s="3"/>
+      <c r="K1834" s="3"/>
+    </row>
+    <row r="1835" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1835" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1835" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1835" s="53">
+        <v>46311</v>
+      </c>
+      <c r="D1835" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1835" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1835" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1835" s="21" t="s">
+        <v>799</v>
+      </c>
+      <c r="H1835" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1835" s="8"/>
+      <c r="J1835" s="8"/>
+      <c r="K1835" s="9" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1836" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1836" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1836" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D1836" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1836" s="51" t="s">
+        <v>759</v>
+      </c>
+      <c r="F1836" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1836" s="12" t="s">
+        <v>800</v>
+      </c>
+      <c r="H1836" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1836" s="3"/>
+      <c r="J1836" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1836" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1837" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1837" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1837" s="53">
+        <v>46311</v>
+      </c>
+      <c r="D1837" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1837" s="55" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1837" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1837" s="21" t="s">
+        <v>801</v>
+      </c>
+      <c r="H1837" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1837" s="8"/>
+      <c r="J1837" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1837" s="9" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1838" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1838" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1838" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D1838" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1838" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1838" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1838" s="12" t="s">
+        <v>802</v>
+      </c>
+      <c r="H1838" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1838" s="3"/>
+      <c r="J1838" s="3"/>
+      <c r="K1838" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1839" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1839" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1839" s="53">
+        <v>46311</v>
+      </c>
+      <c r="D1839" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1839" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1839" s="13"/>
+      <c r="G1839" s="13"/>
+      <c r="H1839" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1839" s="14" t="s">
+        <v>803</v>
+      </c>
+      <c r="J1839" s="13"/>
+      <c r="K1839" s="13"/>
+    </row>
+    <row r="1840" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1840" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1840" s="19" t="s">
+        <v>578</v>
+      </c>
+      <c r="C1840" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D1840" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1840" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="F1840" s="13"/>
+      <c r="G1840" s="13"/>
+      <c r="H1840" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1840" s="14" t="s">
+        <v>803</v>
+      </c>
+      <c r="J1840" s="13"/>
+      <c r="K1840" s="13"/>
+    </row>
+    <row r="1841" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1841" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1841" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1841" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1841" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1841" s="19" t="s">
+        <v>510</v>
+      </c>
+      <c r="F1841" s="19">
+        <v>400943329</v>
+      </c>
+      <c r="G1841" s="15">
+        <v>400943329</v>
+      </c>
+      <c r="H1841" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1841" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="J1841" s="13"/>
+      <c r="K1841" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1842" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1842" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1842" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1842" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1842" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1842" s="57"/>
+      <c r="G1842" s="16"/>
+      <c r="H1842" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1842" s="16"/>
+      <c r="J1842" s="16"/>
+      <c r="K1842" s="16"/>
+    </row>
+    <row r="1843" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1843" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1843" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1843" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1843" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1843" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1843" s="34"/>
+      <c r="G1843" s="13"/>
+      <c r="H1843" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1843" s="14" t="s">
+        <v>804</v>
+      </c>
+      <c r="J1843" s="13"/>
+      <c r="K1843" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1844" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1844" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1844" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1844" s="33" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1844" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1844" s="33">
+        <v>400943329</v>
+      </c>
+      <c r="G1844" s="26">
+        <v>400943329</v>
+      </c>
+      <c r="H1844" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="I1844" s="25" t="s">
+        <v>805</v>
+      </c>
+      <c r="J1844" s="24"/>
+      <c r="K1844" s="25" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1845" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1845" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1845" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1845" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1845" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1845" s="57"/>
+      <c r="G1845" s="16"/>
+      <c r="H1845" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1845" s="16"/>
+      <c r="J1845" s="16"/>
+      <c r="K1845" s="16"/>
+    </row>
+    <row r="1846" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1846" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1846" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1846" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1846" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1846" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1846" s="57"/>
+      <c r="G1846" s="16"/>
+      <c r="H1846" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1846" s="16"/>
+      <c r="J1846" s="16"/>
+      <c r="K1846" s="16"/>
+    </row>
+    <row r="1847" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1847" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1847" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1847" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1847" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1847" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1847" s="7">
+        <v>400945527</v>
+      </c>
+      <c r="G1847" s="21">
+        <v>146616210</v>
+      </c>
+      <c r="H1847" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1847" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="J1847" s="8"/>
+      <c r="K1847" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1848" s="51" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1848" s="51" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1848" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1848" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1848" s="51" t="s">
+        <v>335</v>
+      </c>
+      <c r="F1848" s="7">
+        <v>400945533</v>
+      </c>
+      <c r="G1848" s="7">
+        <v>146615891</v>
+      </c>
+      <c r="H1848" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1848" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="J1848" s="3"/>
+      <c r="K1848" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1849" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1849" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1849" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1849" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1849" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1849" s="7">
+        <v>400945385</v>
+      </c>
+      <c r="G1849" s="7">
+        <v>146613346</v>
+      </c>
+      <c r="H1849" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1849" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="J1849" s="8"/>
+      <c r="K1849" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1850" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1850" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1850" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1850" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1850" s="29" t="s">
+        <v>759</v>
+      </c>
+      <c r="F1850" s="57"/>
+      <c r="G1850" s="16"/>
+      <c r="H1850" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1850" s="16"/>
+      <c r="J1850" s="16"/>
+      <c r="K1850" s="16"/>
+    </row>
+    <row r="1851" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1851" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1851" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1851" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1851" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1851" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1851" s="57"/>
+      <c r="G1851" s="16"/>
+      <c r="H1851" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1851" s="16"/>
+      <c r="J1851" s="16"/>
+      <c r="K1851" s="16"/>
+    </row>
+    <row r="1852" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1852" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1852" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1852" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1852" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1852" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1852" s="57"/>
+      <c r="G1852" s="16"/>
+      <c r="H1852" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1852" s="16"/>
+      <c r="J1852" s="16"/>
+      <c r="K1852" s="16"/>
+    </row>
+    <row r="1853" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1853" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1853" s="55" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1853" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1853" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1853" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1853" s="7">
+        <v>400945384</v>
+      </c>
+      <c r="G1853" s="7">
+        <v>146609490</v>
+      </c>
+      <c r="H1853" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1853" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="J1853" s="8"/>
+      <c r="K1853" s="9" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1854" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1854" s="29" t="s">
+        <v>578</v>
+      </c>
+      <c r="C1854" s="60">
+        <v>46312</v>
+      </c>
+      <c r="D1854" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1854" s="29" t="s">
+        <v>579</v>
+      </c>
+      <c r="F1854" s="57"/>
+      <c r="G1854" s="16"/>
+      <c r="H1854" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1854" s="16"/>
+      <c r="J1854" s="16"/>
+      <c r="K1854" s="16"/>
+    </row>
+    <row r="1855" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1855" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1855" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1855" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1855" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1855" s="29" t="s">
+        <v>510</v>
+      </c>
+      <c r="F1855" s="57"/>
+      <c r="G1855" s="16"/>
+      <c r="H1855" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1855" s="16"/>
+      <c r="J1855" s="16"/>
+      <c r="K1855" s="16"/>
+    </row>
+    <row r="1856" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1856" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1856" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1856" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1856" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1856" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1856" s="57"/>
+      <c r="G1856" s="16"/>
+      <c r="H1856" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1856" s="16"/>
+      <c r="J1856" s="16"/>
+      <c r="K1856" s="16"/>
+    </row>
+    <row r="1857" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1857" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1857" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1857" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1857" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1857" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1857" s="34"/>
+      <c r="G1857" s="13"/>
+      <c r="H1857" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1857" s="14" t="s">
+        <v>804</v>
+      </c>
+      <c r="J1857" s="13"/>
+      <c r="K1857" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1858" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1858" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1858" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1858" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1858" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1858" s="7">
+        <v>146619068</v>
+      </c>
+      <c r="G1858" s="12">
+        <v>146619068</v>
+      </c>
+      <c r="H1858" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1858" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="J1858" s="3"/>
+      <c r="K1858" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1859" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1859" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1859" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1859" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1859" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1859" s="57"/>
+      <c r="G1859" s="16"/>
+      <c r="H1859" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1859" s="16"/>
+      <c r="J1859" s="16"/>
+      <c r="K1859" s="16"/>
+    </row>
+    <row r="1860" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1860" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1860" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1860" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1860" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1860" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1860" s="57"/>
+      <c r="G1860" s="16"/>
+      <c r="H1860" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1860" s="16"/>
+      <c r="J1860" s="16"/>
+      <c r="K1860" s="16"/>
+    </row>
+    <row r="1861" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1861" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1861" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1861" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1861" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1861" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1861" s="7">
+        <v>400945362</v>
+      </c>
+      <c r="G1861" s="7">
+        <v>146604772</v>
+      </c>
+      <c r="H1861" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1861" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="J1861" s="8"/>
+      <c r="K1861" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1862" s="51" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1862" s="51" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1862" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1862" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1862" s="51" t="s">
+        <v>335</v>
+      </c>
+      <c r="F1862" s="7">
+        <v>146615392</v>
+      </c>
+      <c r="G1862" s="7">
+        <v>146615392</v>
+      </c>
+      <c r="H1862" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1862" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1862" s="3"/>
+      <c r="K1862" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1863" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1863" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1863" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1863" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1863" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1863" s="34"/>
+      <c r="G1863" s="34"/>
+      <c r="H1863" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1863" s="14" t="s">
+        <v>807</v>
+      </c>
+      <c r="J1863" s="13"/>
+      <c r="K1863" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1864" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1864" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1864" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1864" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1864" s="29" t="s">
+        <v>759</v>
+      </c>
+      <c r="F1864" s="57"/>
+      <c r="G1864" s="16"/>
+      <c r="H1864" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1864" s="16"/>
+      <c r="J1864" s="16"/>
+      <c r="K1864" s="16"/>
+    </row>
+    <row r="1865" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1865" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1865" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1865" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1865" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1865" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1865" s="57"/>
+      <c r="G1865" s="16"/>
+      <c r="H1865" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1865" s="16"/>
+      <c r="J1865" s="16"/>
+      <c r="K1865" s="16"/>
+    </row>
+    <row r="1866" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1866" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1866" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1866" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1866" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1866" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1866" s="57"/>
+      <c r="G1866" s="16"/>
+      <c r="H1866" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1866" s="16"/>
+      <c r="J1866" s="16"/>
+      <c r="K1866" s="16"/>
+    </row>
+    <row r="1867" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1867" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1867" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1867" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1867" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1867" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1867" s="34"/>
+      <c r="G1867" s="34"/>
+      <c r="H1867" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1867" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="J1867" s="13"/>
+      <c r="K1867" s="14" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1868" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1868" s="29" t="s">
+        <v>578</v>
+      </c>
+      <c r="C1868" s="61">
+        <v>46313</v>
+      </c>
+      <c r="D1868" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1868" s="29" t="s">
+        <v>579</v>
+      </c>
+      <c r="F1868" s="57"/>
+      <c r="G1868" s="16"/>
+      <c r="H1868" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1868" s="16"/>
+      <c r="J1868" s="16"/>
+      <c r="K1868" s="16"/>
+    </row>
+    <row r="1869" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1869" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1869" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1869" s="53">
+        <v>46314</v>
+      </c>
+      <c r="D1869" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1869" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1869" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1869" s="21" t="s">
+        <v>808</v>
+      </c>
+      <c r="H1869" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1869" s="8"/>
+      <c r="J1869" s="8"/>
+      <c r="K1869" s="8"/>
+    </row>
+    <row r="1870" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1870" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1870" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1870" s="54">
+        <v>46314</v>
+      </c>
+      <c r="D1870" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1870" s="51" t="s">
+        <v>759</v>
+      </c>
+      <c r="F1870" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="G1870" s="12" t="s">
+        <v>809</v>
+      </c>
+      <c r="H1870" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1870" s="3"/>
+      <c r="J1870" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1870" s="3"/>
+    </row>
+    <row r="1871" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1871" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1871" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1871" s="53">
+        <v>46314</v>
+      </c>
+      <c r="D1871" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1871" s="55" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1871" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="G1871" s="21" t="s">
+        <v>811</v>
+      </c>
+      <c r="H1871" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1871" s="8"/>
+      <c r="J1871" s="8"/>
+      <c r="K1871" s="8"/>
+    </row>
+    <row r="1872" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1872" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1872" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1872" s="54">
+        <v>46314</v>
+      </c>
+      <c r="D1872" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1872" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1872" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1872" s="12" t="s">
+        <v>812</v>
+      </c>
+      <c r="H1872" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1872" s="3"/>
+      <c r="J1872" s="3"/>
+      <c r="K1872" s="3"/>
+    </row>
+    <row r="1873" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1873" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1873" s="31" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1873" s="53">
+        <v>46314</v>
+      </c>
+      <c r="D1873" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1873" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1873" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1873" s="21" t="s">
+        <v>813</v>
+      </c>
+      <c r="H1873" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1873" s="8"/>
+      <c r="J1873" s="8"/>
+      <c r="K1873" s="8"/>
+    </row>
+    <row r="1874" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1874" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1874" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="C1874" s="54">
+        <v>46314</v>
+      </c>
+      <c r="D1874" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1874" s="51" t="s">
+        <v>579</v>
+      </c>
+      <c r="F1874" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="G1874" s="12" t="s">
+        <v>814</v>
+      </c>
+      <c r="H1874" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1874" s="3"/>
+      <c r="J1874" s="3"/>
+      <c r="K1874" s="3"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F1410" r:id="rId1" display="http://di.ps/" xr:uid="{3F374B45-1231-48CF-9AFE-3A44DBF64903}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/COPIA PROGRAMADOR SEGUIMIENTO.xlsx
+++ b/COPIA PROGRAMADOR SEGUIMIENTO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\SEGUIMIENTO PRODUCCION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE893DD3-3705-4EEB-A1EB-268A58522EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3500239D-38F4-4B19-AD7D-3C1B2D29C5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C06DA29B-B1D3-475F-97A6-5BB133A5B28B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14207" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14289" uniqueCount="857">
   <si>
     <t>PROCESO</t>
   </si>
@@ -2597,6 +2597,15 @@
   </si>
   <si>
     <t>CONSIGNA PROPUESTA 3 PAYANDE</t>
+  </si>
+  <si>
+    <t>TUTELA</t>
+  </si>
+  <si>
+    <t>IBAGUGE</t>
+  </si>
+  <si>
+    <t>CAMBOIO DE TRAFO</t>
   </si>
 </sst>
 </file>
@@ -3301,7 +3310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B1D2AE4-73A5-4A6B-9021-04AC9E1DF3F4}">
-  <dimension ref="A1:K1912"/>
+  <dimension ref="A1:K1928"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
@@ -58646,9 +58655,7 @@
       </c>
       <c r="H1740" s="3"/>
       <c r="I1740" s="3"/>
-      <c r="J1740" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1740" s="3"/>
       <c r="K1740" s="4" t="s">
         <v>719</v>
       </c>
@@ -58737,9 +58744,7 @@
       </c>
       <c r="H1743" s="8"/>
       <c r="I1743" s="8"/>
-      <c r="J1743" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1743" s="8"/>
       <c r="K1743" s="9" t="s">
         <v>719</v>
       </c>
@@ -59955,9 +59960,7 @@
       <c r="I1783" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="J1783" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1783" s="8"/>
       <c r="K1783" s="9" t="s">
         <v>719</v>
       </c>
@@ -60095,9 +60098,7 @@
       <c r="I1787" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="J1787" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1787" s="8"/>
       <c r="K1787" s="9" t="s">
         <v>719</v>
       </c>
@@ -60410,9 +60411,7 @@
       <c r="I1796" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="J1796" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1796" s="3"/>
       <c r="K1796" s="4" t="s">
         <v>719</v>
       </c>
@@ -60445,9 +60444,7 @@
       <c r="I1797" s="9" t="s">
         <v>771</v>
       </c>
-      <c r="J1797" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1797" s="8"/>
       <c r="K1797" s="9" t="s">
         <v>719</v>
       </c>
@@ -60515,9 +60512,7 @@
       <c r="I1799" s="9" t="s">
         <v>771</v>
       </c>
-      <c r="J1799" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1799" s="8"/>
       <c r="K1799" s="9" t="s">
         <v>719</v>
       </c>
@@ -60550,9 +60545,7 @@
       <c r="I1800" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="J1800" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1800" s="3"/>
       <c r="K1800" s="4" t="s">
         <v>719</v>
       </c>
@@ -60585,9 +60578,7 @@
       <c r="I1801" s="9" t="s">
         <v>771</v>
       </c>
-      <c r="J1801" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1801" s="8"/>
       <c r="K1801" s="9" t="s">
         <v>719</v>
       </c>
@@ -61005,9 +60996,7 @@
       <c r="I1813" s="9" t="s">
         <v>787</v>
       </c>
-      <c r="J1813" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1813" s="8"/>
       <c r="K1813" s="9" t="s">
         <v>719</v>
       </c>
@@ -61040,9 +61029,7 @@
       <c r="I1814" s="4" t="s">
         <v>789</v>
       </c>
-      <c r="J1814" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1814" s="3"/>
       <c r="K1814" s="4" t="s">
         <v>719</v>
       </c>
@@ -61145,9 +61132,7 @@
       <c r="I1817" s="9" t="s">
         <v>787</v>
       </c>
-      <c r="J1817" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1817" s="8"/>
       <c r="K1817" s="9" t="s">
         <v>719</v>
       </c>
@@ -61804,9 +61789,7 @@
       <c r="I1836" s="4" t="s">
         <v>824</v>
       </c>
-      <c r="J1836" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1836" s="3"/>
       <c r="K1836" s="4" t="s">
         <v>491</v>
       </c>
@@ -61839,9 +61822,7 @@
       <c r="I1837" s="9" t="s">
         <v>824</v>
       </c>
-      <c r="J1837" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1837" s="8"/>
       <c r="K1837" s="9" t="s">
         <v>491</v>
       </c>
@@ -62836,9 +62817,7 @@
       <c r="I1870" s="4" t="s">
         <v>826</v>
       </c>
-      <c r="J1870" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1870" s="3"/>
       <c r="K1870" s="4" t="s">
         <v>719</v>
       </c>
@@ -63361,9 +63340,7 @@
       <c r="I1885" s="9" t="s">
         <v>826</v>
       </c>
-      <c r="J1885" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1885" s="8"/>
       <c r="K1885" s="9" t="s">
         <v>719</v>
       </c>
@@ -63396,9 +63373,7 @@
       <c r="I1886" s="4" t="s">
         <v>826</v>
       </c>
-      <c r="J1886" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1886" s="3"/>
       <c r="K1886" s="4" t="s">
         <v>719</v>
       </c>
@@ -63676,7 +63651,9 @@
       <c r="I1894" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="J1894" s="3"/>
+      <c r="J1894" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="K1894" s="4" t="s">
         <v>287</v>
       </c>
@@ -63837,12 +63814,22 @@
       <c r="E1899" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="F1899" s="8"/>
-      <c r="G1899" s="8"/>
-      <c r="H1899" s="8"/>
-      <c r="I1899" s="8"/>
+      <c r="F1899" s="9">
+        <v>400946753</v>
+      </c>
+      <c r="G1899" s="21">
+        <v>146621698</v>
+      </c>
+      <c r="H1899" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1899" s="9" t="s">
+        <v>592</v>
+      </c>
       <c r="J1899" s="8"/>
-      <c r="K1899" s="8"/>
+      <c r="K1899" s="9" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="1900" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1900" s="7" t="s">
@@ -63872,9 +63859,7 @@
       <c r="I1900" s="4" t="s">
         <v>826</v>
       </c>
-      <c r="J1900" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1900" s="3"/>
       <c r="K1900" s="3"/>
     </row>
     <row r="1901" spans="1:11" x14ac:dyDescent="0.25">
@@ -63905,9 +63890,7 @@
       <c r="I1901" s="9" t="s">
         <v>826</v>
       </c>
-      <c r="J1901" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="J1901" s="8"/>
       <c r="K1901" s="8"/>
     </row>
     <row r="1902" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -64102,12 +64085,14 @@
         <v>840</v>
       </c>
       <c r="H1907" s="9" t="s">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="I1907" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="J1907" s="8"/>
+      <c r="J1907" s="9" t="s">
+        <v>185</v>
+      </c>
       <c r="K1907" s="9" t="s">
         <v>251</v>
       </c>
@@ -64140,7 +64125,9 @@
       <c r="I1908" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="J1908" s="3"/>
+      <c r="J1908" s="4" t="s">
+        <v>185</v>
+      </c>
       <c r="K1908" s="4" t="s">
         <v>236</v>
       </c>
@@ -64284,6 +64271,450 @@
       <c r="K1912" s="14" t="s">
         <v>287</v>
       </c>
+    </row>
+    <row r="1913" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1913" s="58"/>
+      <c r="B1913" s="58"/>
+      <c r="C1913" s="58"/>
+      <c r="D1913" s="58"/>
+      <c r="E1913" s="58"/>
+      <c r="F1913" s="58"/>
+      <c r="G1913" s="58"/>
+      <c r="H1913" s="58"/>
+      <c r="I1913" s="58"/>
+      <c r="J1913" s="58"/>
+      <c r="K1913" s="58"/>
+    </row>
+    <row r="1914" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1914" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1914" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1914" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1914" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1914" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1914" s="44"/>
+      <c r="G1914" s="3"/>
+      <c r="H1914" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1914" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="J1914" s="3"/>
+      <c r="K1914" s="4" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1915" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1915" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1915" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1915" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1915" s="55" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1915" s="44"/>
+      <c r="G1915" s="8"/>
+      <c r="H1915" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1915" s="9" t="s">
+        <v>826</v>
+      </c>
+      <c r="J1915" s="8"/>
+      <c r="K1915" s="9" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1916" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1916" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1916" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1916" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1916" s="51" t="s">
+        <v>759</v>
+      </c>
+      <c r="F1916" s="44"/>
+      <c r="G1916" s="3"/>
+      <c r="H1916" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1916" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="J1916" s="3"/>
+      <c r="K1916" s="4" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1917" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1917" s="31" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1917" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1917" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1917" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1917" s="44"/>
+      <c r="G1917" s="8"/>
+      <c r="H1917" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1917" s="9" t="s">
+        <v>827</v>
+      </c>
+      <c r="J1917" s="8"/>
+      <c r="K1917" s="9" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1918" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1918" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="C1918" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1918" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1918" s="51" t="s">
+        <v>579</v>
+      </c>
+      <c r="F1918" s="44"/>
+      <c r="G1918" s="3"/>
+      <c r="H1918" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1918" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="J1918" s="3"/>
+      <c r="K1918" s="4" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1919" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1919" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1919" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1919" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1919" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1919" s="8"/>
+      <c r="G1919" s="8"/>
+      <c r="H1919" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1919" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="J1919" s="8"/>
+      <c r="K1919" s="9" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1920" s="51" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1920" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1920" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1920" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1920" s="51" t="s">
+        <v>510</v>
+      </c>
+      <c r="F1920" s="7">
+        <v>400946812</v>
+      </c>
+      <c r="G1920" s="7">
+        <v>400946812</v>
+      </c>
+      <c r="H1920" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1920" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="J1920" s="3"/>
+      <c r="K1920" s="4" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1921" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1921" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1921" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1921" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1921" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1921" s="7">
+        <v>400946662</v>
+      </c>
+      <c r="G1921" s="21">
+        <v>146620398</v>
+      </c>
+      <c r="H1921" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1921" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="J1921" s="8"/>
+      <c r="K1921" s="9" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1922" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1922" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1922" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1922" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1922" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1922" s="7">
+        <v>400946797</v>
+      </c>
+      <c r="G1922" s="12">
+        <v>146620973</v>
+      </c>
+      <c r="H1922" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1922" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="J1922" s="3"/>
+      <c r="K1922" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1923" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1923" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1923" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1923" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1923" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1923" s="44"/>
+      <c r="G1923" s="8"/>
+      <c r="H1923" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1923" s="8"/>
+      <c r="J1923" s="8"/>
+      <c r="K1923" s="8"/>
+    </row>
+    <row r="1924" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1924" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1924" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1924" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1924" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1924" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1924" s="44"/>
+      <c r="G1924" s="3"/>
+      <c r="H1924" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1924" s="3"/>
+      <c r="J1924" s="3"/>
+      <c r="K1924" s="3"/>
+    </row>
+    <row r="1925" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1925" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1925" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1925" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1925" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1925" s="55" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1925" s="7">
+        <v>400946789</v>
+      </c>
+      <c r="G1925" s="21">
+        <v>146618468</v>
+      </c>
+      <c r="H1925" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1925" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="J1925" s="8"/>
+      <c r="K1925" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1926" s="51" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1926" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1926" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1926" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1926" s="51" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1926" s="44"/>
+      <c r="G1926" s="44"/>
+      <c r="H1926" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1926" s="3"/>
+      <c r="J1926" s="3"/>
+      <c r="K1926" s="3"/>
+    </row>
+    <row r="1927" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1927" s="55" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1927" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1927" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1927" s="55" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1927" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1927" s="44"/>
+      <c r="G1927" s="44"/>
+      <c r="H1927" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1927" s="8"/>
+      <c r="J1927" s="8"/>
+      <c r="K1927" s="8"/>
+    </row>
+    <row r="1928" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1928" s="51" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1928" s="51" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1928" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D1928" s="51" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1928" s="51" t="s">
+        <v>335</v>
+      </c>
+      <c r="F1928" s="44"/>
+      <c r="G1928" s="44"/>
+      <c r="H1928" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1928" s="3"/>
+      <c r="J1928" s="3"/>
+      <c r="K1928" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
